--- a/dados/dados.xlsx
+++ b/dados/dados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\04 - Relatórios\Relatórios ROTINA\02 - Relatórios\2026\05 - Maio\ROTINA 2026_05_11\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\04 - Relatórios\Relatórios ROTINA\02 - Relatórios\2026\06 - Junho\ROTINA 2026_06_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4828AA-9E77-44C8-A9D7-456A37684420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF77DB73-6196-44A4-925E-C8299DCD4D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="307">
   <si>
     <t>INDICADOR</t>
   </si>
@@ -47,7 +47,7 @@
     <t>1. QUANTIDADE DE ESCOLAS NA REDE</t>
   </si>
   <si>
-    <t>1.1. QUANTIDADE DE ESCOLAS COM MATRÍCULA ATIVA EM 11/05/2026</t>
+    <t>1.1. QUANTIDADE DE ESCOLAS COM MATRÍCULA ATIVA EM 01/06/2026</t>
   </si>
   <si>
     <t>1.1.1. Quantidade de escolas com oferta de Ensino Fundamental</t>
@@ -92,6 +92,54 @@
     <t>1.1.4.6. Quantidade de escolas com oferta de Curso técnico integrado na modalidade EJA</t>
   </si>
   <si>
+    <t>1.2 Quantidade de escolas localizadas em Zona Urbana</t>
+  </si>
+  <si>
+    <t>1.3 Quantidade de escolas localizadas em Zona Rural</t>
+  </si>
+  <si>
+    <t>1.4 Quantidade de escolas com oferta de turno de Tempo Integral</t>
+  </si>
+  <si>
+    <t>1.4.1 Quantidade de escolas com oferta de turno Integral 7h - Manhã</t>
+  </si>
+  <si>
+    <t>1.4.2 Quantidade de escolas com oferta de turno Integral 7h - Tarde</t>
+  </si>
+  <si>
+    <t>1.4.3 Quantidade de escolas com oferta de turno Integral 8h</t>
+  </si>
+  <si>
+    <t>1.4.4 Quantidade de escolas com oferta de turno Integral 9h30min</t>
+  </si>
+  <si>
+    <t>1.5 Quantidade de escolas com oferta de turno de Tempo Parcial</t>
+  </si>
+  <si>
+    <t>1.5.1 Quantidade de escolas com oferta do turno Manhã</t>
+  </si>
+  <si>
+    <t>1.5.2 Quantidade de escolas com oferta do turno Tarde</t>
+  </si>
+  <si>
+    <t>1.5.3 Quantidade de escolas com oferta do turno Noite</t>
+  </si>
+  <si>
+    <t>1.6 Quantidade de escolas com localização diferenciada conforme indicado no CENSO ESCOLAR</t>
+  </si>
+  <si>
+    <t>1.6.1 Quantidade de escolas em 'Área de assentamento'</t>
+  </si>
+  <si>
+    <t>1.6.2 Quantidade de escolas em 'Área onde se localizam povos e comunidades tradicionais'</t>
+  </si>
+  <si>
+    <t>1.6.3 Quantidade de escolas em 'Comunidade quilombola'</t>
+  </si>
+  <si>
+    <t>1.6.4 Quantidade de escolas em 'Terra indígena'</t>
+  </si>
+  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -278,6 +326,54 @@
     <t>2.3.4.6.3. Quantidade de turmas de 3ª Etapa do Curso técnico integrado na modalidade EJA</t>
   </si>
   <si>
+    <t>2.4 Quantidade de turmas em escolas localizadas em Zona Urbana</t>
+  </si>
+  <si>
+    <t>2.5 Quantidade de turmas em escolas localizadas em Zona Rural</t>
+  </si>
+  <si>
+    <t>2.6 Quantidade de turmas de turno de Tempo Integral</t>
+  </si>
+  <si>
+    <t>2.6.1 Quantidade de turmas de turno Integral 7h - Manhã</t>
+  </si>
+  <si>
+    <t>2.6.2 Quantidade de turmas de turno Integral 7h - Tarde</t>
+  </si>
+  <si>
+    <t>2.6.3 Quantidade de turmas de turno Integral 8h</t>
+  </si>
+  <si>
+    <t>2.6.4 Quantidade de turmas de turno Integral 9h30min</t>
+  </si>
+  <si>
+    <t>2.7 Quantidade de turmas de turno de Tempo Parcial</t>
+  </si>
+  <si>
+    <t>2.7.1 Quantidade de turmas de turno Manhã</t>
+  </si>
+  <si>
+    <t>2.7.2 Quantidade de turmas de turno Tarde</t>
+  </si>
+  <si>
+    <t>2.7.3 Quantidade de turmas de turno Noite</t>
+  </si>
+  <si>
+    <t>2.8 Quantidade de turmas em escolas com localização diferenciada conforme indicado no CENSO ESCOLAR</t>
+  </si>
+  <si>
+    <t>2.8.1 Quantidade de turmas em escolas em 'Área de assentamento'</t>
+  </si>
+  <si>
+    <t>2.8.2 Quantidade de turmas em escolas em 'Área onde se localizam povos e comunidades tradicionais'</t>
+  </si>
+  <si>
+    <t>2.8.3 Quantidade de turmas em escolas em 'Comunidade quilombola'</t>
+  </si>
+  <si>
+    <t>2.8.4 Quantidade de turmas em escolas em 'Terra indígena'</t>
+  </si>
+  <si>
     <t>3. QUANTIDADE DE MATRÍCULAS</t>
   </si>
   <si>
@@ -494,6 +590,84 @@
     <t>4.7.6.3. Quantidade de alunos na 3ª Etapa do Curso técnico integrado na modalidade EJA</t>
   </si>
   <si>
+    <t>4.8 Quantidade de alunos público-alvo da Educação Especial (alunos com deficiência)</t>
+  </si>
+  <si>
+    <t>4.9 Quantidade de alunos com raça/cor declarada - Amarela</t>
+  </si>
+  <si>
+    <t>4.10 Quantidade de alunos com raça/cor declarada - Branca</t>
+  </si>
+  <si>
+    <t>4.11 Quantidade de alunos com raça/cor declarada - Indígena</t>
+  </si>
+  <si>
+    <t>4.12 Quantidade de alunos com raça/cor declarada - Parda</t>
+  </si>
+  <si>
+    <t>4.13 Quantidade de alunos com raça/cor declarada - Preta</t>
+  </si>
+  <si>
+    <t>4.14 Quantidade de alunos com raça/cor não declarada</t>
+  </si>
+  <si>
+    <t>4.15 Quantidade de alunos do sexo Feminino</t>
+  </si>
+  <si>
+    <t>4.16 Quantidade de alunos do sexo Masculino</t>
+  </si>
+  <si>
+    <t>4.17 Quantidade de alunos com sexo não informado</t>
+  </si>
+  <si>
+    <t>4.18 Quantidade de alunos em escolas localizadas em Zona Urbana</t>
+  </si>
+  <si>
+    <t>4.19 Quantidade de alunos em escolas localizadas em Zona Rural</t>
+  </si>
+  <si>
+    <t>4.20 Quantidade de alunos em turmas de turno de Tempo Integral</t>
+  </si>
+  <si>
+    <t>4.20.1 Quantidade de alunos em turmas de turno Integral 7h - Manhã</t>
+  </si>
+  <si>
+    <t>4.20.2 Quantidade de alunos em turmas de turno Integral 7h - Tarde</t>
+  </si>
+  <si>
+    <t>4.20.3 Quantidade de alunos em turmas de turno Integral 8h</t>
+  </si>
+  <si>
+    <t>4.20.4 Quantidade de alunos em turmas de turno Integral 9h30min</t>
+  </si>
+  <si>
+    <t>4.21 Quantidade de alunos em turmas de turno de Tempo Parcial</t>
+  </si>
+  <si>
+    <t>4.21.1 Quantidade de alunos em turmas de turno Manhã</t>
+  </si>
+  <si>
+    <t>4.21.2 Quantidade de alunos em turmas de turno Tarde</t>
+  </si>
+  <si>
+    <t>4.21.2 Quantidade de alunos em turmas de turno Noite</t>
+  </si>
+  <si>
+    <t>4.22 Quantidade de alunos em escolas com localização diferenciada conforme indicado no CENSO ESCOLAR</t>
+  </si>
+  <si>
+    <t>4.22.1 Quantidade de alunos em escolas em 'Área de assentamento'</t>
+  </si>
+  <si>
+    <t>4.22.2 Quantidade de alunos em escolas em 'Área onde se localizam povos e comunidades tradicionais'</t>
+  </si>
+  <si>
+    <t>4.22.2 Quantidade de alunos em escolas em 'Comunidade quilombola'</t>
+  </si>
+  <si>
+    <t>4.22.2 Quantidade de alunos em escolas em 'Terra indígena'</t>
+  </si>
+  <si>
     <t>5. QUANTIDADE DE DOCENTES</t>
   </si>
   <si>
@@ -698,13 +872,88 @@
     <t>5.7.6.3. Quantidade de docentes na 3ª Etapa do Curso técnico integrado na modalidade EJA</t>
   </si>
   <si>
+    <t>5.8 Quantidade de docentes com raça/cor declarada - Amarela</t>
+  </si>
+  <si>
+    <t>5.9 Quantidade de docentes com raça/cor declarada - Branca</t>
+  </si>
+  <si>
+    <t>5.10 Quantidade de docentes com raça/cor declarada - Indígena</t>
+  </si>
+  <si>
+    <t>5.11 Quantidade de docentes com raça/cor declarada - Parda</t>
+  </si>
+  <si>
+    <t>5.12 Quantidade de docentes com raça/cor declarada - Preta</t>
+  </si>
+  <si>
+    <t>5.13 Quantidade de docentes com raça/cor não declarada</t>
+  </si>
+  <si>
+    <t>5.14 Quantidade de docentes do sexo Feminino</t>
+  </si>
+  <si>
+    <t>5.15 Quantidade de docentes do sexo Masculino</t>
+  </si>
+  <si>
+    <t>5.16 Quantidade de docentes com sexo não informado</t>
+  </si>
+  <si>
+    <t>5.17 Quantidade de docentes em escolas localizadas em Zona Urbana</t>
+  </si>
+  <si>
+    <t>5.18 Quantidade de docentes em escolas localizadas em Zona Rural</t>
+  </si>
+  <si>
+    <t>5.19 Quantidade de docentes em turmas de turno de Tempo Integral</t>
+  </si>
+  <si>
+    <t>5.19.1 Quantidade de docentes em turmas de turno Integral 7h - Manhã</t>
+  </si>
+  <si>
+    <t>5.19.2 Quantidade de docentes em turmas de turno Integral 7h - Tarde</t>
+  </si>
+  <si>
+    <t>5.19.3 Quantidade de docentes em turmas de turno Integral 8h</t>
+  </si>
+  <si>
+    <t>5.19.4 Quantidade de docentes em turmas de turno Integral 9h30min</t>
+  </si>
+  <si>
+    <t>5.20 Quantidade de docentes em turmas de turno de Tempo Parcial</t>
+  </si>
+  <si>
+    <t>5.20.1 Quantidade de docentes em turmas de turno Manhã</t>
+  </si>
+  <si>
+    <t>5.20.2 Quantidade de docentes em turmas de turno Tarde</t>
+  </si>
+  <si>
+    <t>5.20.3 Quantidade de docentes em turmas de turno Noite</t>
+  </si>
+  <si>
+    <t>5.21 Quantidade de docentes em escolas com localização diferenciada conforme indicado no CENSO ESCOLAR</t>
+  </si>
+  <si>
+    <t>5.21.1 Quantidade de docentes em escolas em 'Área de assentamento'</t>
+  </si>
+  <si>
+    <t>5.21.2 Quantidade de docentes em escolas em 'Área onde se localizam povos e comunidades tradicionais'</t>
+  </si>
+  <si>
+    <t>5.21.3 Quantidade de docentes em escolas em 'Comunidade quilombola'</t>
+  </si>
+  <si>
+    <t>5.21.4 Quantidade de docentes em escolas em 'Terra indígena'</t>
+  </si>
+  <si>
     <t>SÍNTESE GERAL DA REDE ESTADUAL DE ENSINO</t>
   </si>
   <si>
     <t>FONTE: SEGES</t>
   </si>
   <si>
-    <t>DATA: 11/05/2026</t>
+    <t>DATA: 01/06/2026</t>
   </si>
   <si>
     <t>GEI/SEE/EAARAÚJO</t>
@@ -716,9 +965,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -754,6 +1003,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
@@ -858,7 +1114,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -883,17 +1139,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -932,7 +1190,7 @@
         <xdr:cNvPr id="3" name="Imagem 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C135CA32-E0CC-7064-9E5F-C56DF7C33E73}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9441767F-3C14-2DD1-3E51-46F1327EFB43}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1240,11 +1498,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C231"/>
+  <dimension ref="A1:C314"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="16.5" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="106" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="109.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" style="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3.7109375" style="1" customWidth="1"/>
     <col min="4" max="16384" width="11.42578125" style="8" hidden="1"/>
   </cols>
@@ -1252,10 +1510,10 @@
     <row r="1" spans="1:3" s="1" customFormat="1" ht="82.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:3" s="1" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:3" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="B3" s="12"/>
+      <c r="A3" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="B3" s="16"/>
       <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1268,27 +1526,29 @@
       </c>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="18">
         <v>384</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
+      <c r="C6" s="19"/>
+    </row>
+    <row r="7" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="22">
         <v>383</v>
       </c>
+      <c r="C7" s="19"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="12">
         <v>267</v>
       </c>
     </row>
@@ -1296,7 +1556,7 @@
       <c r="A9" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="12">
         <v>98</v>
       </c>
     </row>
@@ -1304,7 +1564,7 @@
       <c r="A10" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="12">
         <v>235</v>
       </c>
     </row>
@@ -1312,7 +1572,7 @@
       <c r="A11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="12">
         <v>288</v>
       </c>
     </row>
@@ -1320,7 +1580,7 @@
       <c r="A12" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="12">
         <v>280</v>
       </c>
     </row>
@@ -1328,7 +1588,7 @@
       <c r="A13" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="12">
         <v>148</v>
       </c>
     </row>
@@ -1336,7 +1596,7 @@
       <c r="A14" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="12">
         <v>18</v>
       </c>
     </row>
@@ -1344,7 +1604,7 @@
       <c r="A15" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="12">
         <v>171</v>
       </c>
     </row>
@@ -1352,7 +1612,7 @@
       <c r="A16" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="12">
         <v>26</v>
       </c>
     </row>
@@ -1360,7 +1620,7 @@
       <c r="A17" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="12">
         <v>94</v>
       </c>
     </row>
@@ -1368,7 +1628,7 @@
       <c r="A18" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="12">
         <v>139</v>
       </c>
     </row>
@@ -1376,7 +1636,7 @@
       <c r="A19" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="12">
         <v>2</v>
       </c>
     </row>
@@ -1384,15 +1644,15 @@
       <c r="A20" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="13">
-        <v>34</v>
+      <c r="B20" s="12">
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="12">
         <v>6</v>
       </c>
     </row>
@@ -1400,1668 +1660,2336 @@
       <c r="A22" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="13" t="s">
-        <v>18</v>
+      <c r="B22" s="12">
+        <v>306</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="20">
-        <v>13370</v>
+      <c r="B23" s="12">
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="13">
-        <v>5626</v>
+      <c r="B24" s="12">
+        <v>234</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="13">
-        <v>577</v>
+      <c r="B25" s="12">
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="13">
-        <v>7167</v>
+      <c r="B26" s="12">
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="13">
-        <v>2516</v>
+      <c r="B27" s="12">
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="13">
-        <v>643</v>
+      <c r="B28" s="12">
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="13">
-        <v>123</v>
+      <c r="B29" s="12">
+        <v>355</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="13">
-        <v>131</v>
+      <c r="B30" s="12">
+        <v>221</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="13">
-        <v>131</v>
+      <c r="B31" s="12">
+        <v>233</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="13">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B32" s="12">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B33" s="13">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B33" s="12">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B34" s="13">
-        <v>1873</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B34" s="12">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B35" s="13">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B35" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B36" s="13">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B36" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B37" s="13">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B37" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B38" s="13">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="9" t="s">
+      <c r="B38" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B39" s="13">
-        <v>3477</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B39" s="22">
+        <v>14664</v>
+      </c>
+      <c r="C39" s="19"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="13">
-        <v>2635</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B40" s="12">
+        <v>6773</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="13">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B41" s="12">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B42" s="13">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B42" s="12">
+        <v>7179</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="13">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B43" s="12">
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B44" s="12">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B45" s="13">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B45" s="12">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B46" s="13">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B46" s="12">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="13">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B47" s="12">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="13">
-        <v>276</v>
+      <c r="B48" s="12">
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B49" s="13">
-        <v>0</v>
+      <c r="B49" s="12">
+        <v>134</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B50" s="13">
-        <v>18</v>
+      <c r="B50" s="12">
+        <v>1874</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="13">
-        <v>0</v>
+      <c r="B51" s="12">
+        <v>446</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B52" s="13">
-        <v>18</v>
+      <c r="B52" s="12">
+        <v>453</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="13">
-        <v>0</v>
+      <c r="B53" s="12">
+        <v>461</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B54" s="13">
-        <v>0</v>
+      <c r="B54" s="12">
+        <v>514</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B55" s="13">
-        <v>1156</v>
+      <c r="B55" s="12">
+        <v>3465</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B56" s="13">
-        <v>172</v>
+      <c r="B56" s="12">
+        <v>2626</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B57" s="13">
-        <v>38</v>
+      <c r="B57" s="12">
+        <v>942</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B58" s="13">
-        <v>43</v>
+      <c r="B58" s="12">
+        <v>886</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B59" s="13">
-        <v>44</v>
+      <c r="B59" s="12">
+        <v>798</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B60" s="13">
-        <v>47</v>
+      <c r="B60" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B61" s="13">
-        <v>444</v>
+      <c r="B61" s="12">
+        <v>839</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B62" s="13">
-        <v>96</v>
+      <c r="B62" s="12">
+        <v>286</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B63" s="13">
-        <v>107</v>
+      <c r="B63" s="12">
+        <v>279</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B64" s="13">
-        <v>120</v>
+      <c r="B64" s="12">
+        <v>274</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B65" s="13">
-        <v>121</v>
+      <c r="B65" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B66" s="13">
-        <v>424</v>
+      <c r="B66" s="12">
+        <v>18</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B67" s="13">
-        <v>131</v>
+      <c r="B67" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B68" s="13">
-        <v>135</v>
+      <c r="B68" s="12">
+        <v>18</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B69" s="13">
-        <v>158</v>
+      <c r="B69" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B70" s="13">
-        <v>8</v>
+      <c r="B70" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B71" s="13">
-        <v>2</v>
+      <c r="B71" s="12">
+        <v>1178</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B72" s="13">
-        <v>2</v>
+      <c r="B72" s="12">
+        <v>177</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B73" s="13">
-        <v>2</v>
+      <c r="B73" s="12">
+        <v>41</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="B74" s="13">
-        <v>2</v>
+      <c r="B74" s="12">
+        <v>45</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B75" s="13">
-        <v>98</v>
+      <c r="B75" s="12">
+        <v>43</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B76" s="13">
-        <v>31</v>
+      <c r="B76" s="12">
+        <v>48</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B77" s="13">
-        <v>33</v>
+      <c r="B77" s="12">
+        <v>449</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B78" s="13">
-        <v>34</v>
+      <c r="B78" s="12">
+        <v>96</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B79" s="13">
-        <v>0</v>
+      <c r="B79" s="12">
+        <v>107</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B80" s="13">
-        <v>10</v>
+      <c r="B80" s="12">
+        <v>121</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B81" s="13">
-        <v>4</v>
+      <c r="B81" s="12">
+        <v>125</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B82" s="13">
-        <v>5</v>
+      <c r="B82" s="12">
+        <v>434</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B83" s="13">
-        <v>1</v>
+      <c r="B83" s="12">
+        <v>134</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B84" s="13" t="s">
-        <v>18</v>
+        <v>80</v>
+      </c>
+      <c r="B84" s="12">
+        <v>137</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="B85" s="20">
-        <v>212346</v>
+      <c r="A85" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B85" s="12">
+        <v>163</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B86" s="13">
-        <v>184958</v>
+        <v>82</v>
+      </c>
+      <c r="B86" s="12">
+        <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="B87" s="13">
-        <v>14625</v>
+        <v>83</v>
+      </c>
+      <c r="B87" s="12">
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B88" s="13">
-        <v>12763</v>
+        <v>84</v>
+      </c>
+      <c r="B88" s="12">
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B89" s="13" t="s">
-        <v>18</v>
+        <v>85</v>
+      </c>
+      <c r="B89" s="12">
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A90" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="B90" s="20">
-        <v>184839</v>
+      <c r="A90" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B90" s="12">
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B91" s="13">
-        <v>9090</v>
+        <v>87</v>
+      </c>
+      <c r="B91" s="12">
+        <v>99</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B92" s="13">
-        <v>11958</v>
+        <v>88</v>
+      </c>
+      <c r="B92" s="12">
+        <v>30</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B93" s="13">
-        <v>184593</v>
+        <v>89</v>
+      </c>
+      <c r="B93" s="12">
+        <v>34</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="B94" s="13">
-        <v>51938</v>
+        <v>90</v>
+      </c>
+      <c r="B94" s="12">
+        <v>35</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B95" s="13">
-        <v>48983</v>
+        <v>91</v>
+      </c>
+      <c r="B95" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B96" s="13">
-        <v>13255</v>
+        <v>92</v>
+      </c>
+      <c r="B96" s="12">
+        <v>11</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B97" s="13">
-        <v>48989</v>
+        <v>93</v>
+      </c>
+      <c r="B97" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="B98" s="13">
-        <v>15270</v>
+        <v>94</v>
+      </c>
+      <c r="B98" s="12">
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B99" s="13">
-        <v>170</v>
+        <v>95</v>
+      </c>
+      <c r="B99" s="12">
+        <v>2</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B100" s="13">
-        <v>6353</v>
+        <v>96</v>
+      </c>
+      <c r="B100" s="12">
+        <v>13328</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="B101" s="13">
-        <v>63543</v>
+        <v>97</v>
+      </c>
+      <c r="B101" s="12">
+        <v>1336</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B102" s="13">
-        <v>10859</v>
+        <v>98</v>
+      </c>
+      <c r="B102" s="12">
+        <v>2397</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="B103" s="13">
-        <v>1950</v>
+        <v>99</v>
+      </c>
+      <c r="B103" s="12">
+        <v>1639</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B104" s="13">
-        <v>2155</v>
+        <v>100</v>
+      </c>
+      <c r="B104" s="12">
+        <v>485</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="B105" s="13">
-        <v>2141</v>
+        <v>101</v>
+      </c>
+      <c r="B105" s="12">
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="B106" s="13">
-        <v>2138</v>
+        <v>102</v>
+      </c>
+      <c r="B106" s="12">
+        <v>265</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B107" s="13">
-        <v>2475</v>
+        <v>103</v>
+      </c>
+      <c r="B107" s="12">
+        <v>4782</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="B108" s="13">
-        <v>52684</v>
+        <v>104</v>
+      </c>
+      <c r="B108" s="12">
+        <v>1959</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="B109" s="13">
-        <v>12305</v>
+        <v>105</v>
+      </c>
+      <c r="B109" s="12">
+        <v>1932</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="B110" s="13">
-        <v>12548</v>
+        <v>106</v>
+      </c>
+      <c r="B110" s="12">
+        <v>891</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="B111" s="13">
-        <v>13198</v>
+        <v>107</v>
+      </c>
+      <c r="B111" s="12">
+        <v>642</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="B112" s="13">
-        <v>14633</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+      <c r="B112" s="12">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="B113" s="13">
-        <v>107366</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="B113" s="12">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B114" s="13">
-        <v>81894</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="B114" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="B115" s="13">
-        <v>30382</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+      <c r="B115" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B116" s="13">
-        <v>28199</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A117" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="B117" s="13">
-        <v>23313</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="B116" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="B117" s="22">
+        <v>216285</v>
+      </c>
+      <c r="C117" s="19"/>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B118" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+      <c r="B118" s="12">
+        <v>182415</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="B119" s="13">
-        <v>25472</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+      <c r="B119" s="12">
+        <v>18299</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B120" s="13">
-        <v>10053</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+      <c r="B120" s="12">
+        <v>15571</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="B121" s="13">
-        <v>8161</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A122" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B121" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B122" s="13">
-        <v>7258</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B122" s="22">
+        <v>182400</v>
+      </c>
+      <c r="C122" s="19"/>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="B123" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B123" s="12">
+        <v>10350</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B124" s="13">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B124" s="12">
+        <v>14360</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B125" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B125" s="12">
+        <v>182057</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B126" s="13">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B126" s="12">
+        <v>51449</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B127" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B127" s="12">
+        <v>48238</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B128" s="13">
-        <v>0</v>
+      <c r="B128" s="12">
+        <v>12973</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B129" s="13">
-        <v>13678</v>
+      <c r="B129" s="12">
+        <v>48374</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B130" s="13">
-        <v>767</v>
+      <c r="B130" s="12">
+        <v>14953</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B131" s="13">
-        <v>137</v>
+      <c r="B131" s="12">
+        <v>167</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B132" s="13">
-        <v>179</v>
+      <c r="B132" s="12">
+        <v>6261</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B133" s="13">
-        <v>206</v>
+      <c r="B133" s="12">
+        <v>63154</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B134" s="13">
-        <v>245</v>
+      <c r="B134" s="12">
+        <v>10858</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B135" s="13">
-        <v>3669</v>
+      <c r="B135" s="12">
+        <v>1938</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="B136" s="13">
-        <v>550</v>
+      <c r="B136" s="12">
+        <v>2157</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="B137" s="13">
-        <v>720</v>
+      <c r="B137" s="12">
+        <v>2142</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B138" s="13">
-        <v>1095</v>
+      <c r="B138" s="12">
+        <v>2132</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B139" s="13">
-        <v>1304</v>
+      <c r="B139" s="12">
+        <v>2489</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B140" s="13">
-        <v>7111</v>
+      <c r="B140" s="12">
+        <v>52296</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="B141" s="13">
-        <v>1678</v>
+      <c r="B141" s="12">
+        <v>12278</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B142" s="13">
-        <v>2184</v>
+      <c r="B142" s="12">
+        <v>12492</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="B143" s="13">
-        <v>3249</v>
+      <c r="B143" s="12">
+        <v>13115</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="B144" s="13">
-        <v>70</v>
+      <c r="B144" s="12">
+        <v>14411</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="B145" s="13">
-        <v>8</v>
+      <c r="B145" s="12">
+        <v>105190</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B146" s="13">
-        <v>16</v>
+      <c r="B146" s="12">
+        <v>80151</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B147" s="13">
-        <v>27</v>
+      <c r="B147" s="12">
+        <v>29938</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B148" s="13">
-        <v>19</v>
+      <c r="B148" s="12">
+        <v>27555</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="B149" s="13">
-        <v>1855</v>
+      <c r="B149" s="12">
+        <v>22658</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="B150" s="13">
-        <v>492</v>
+      <c r="B150" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="B151" s="13">
-        <v>673</v>
+      <c r="B151" s="12">
+        <v>25039</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="B152" s="13">
-        <v>690</v>
+      <c r="B152" s="12">
+        <v>9871</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B153" s="13">
-        <v>0</v>
+      <c r="B153" s="12">
+        <v>8018</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="B154" s="13">
-        <v>206</v>
+      <c r="B154" s="12">
+        <v>7150</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="B155" s="13">
-        <v>96</v>
+      <c r="B155" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="B156" s="13">
-        <v>92</v>
+      <c r="B156" s="12">
+        <v>368</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="B157" s="13">
-        <v>18</v>
+      <c r="B157" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B158" s="13" t="s">
-        <v>18</v>
+        <v>152</v>
+      </c>
+      <c r="B158" s="12">
+        <v>368</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A159" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="B159" s="20">
-        <v>12622</v>
+      <c r="A159" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B159" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="B160" s="13">
-        <v>800</v>
+        <v>154</v>
+      </c>
+      <c r="B160" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="B161" s="13">
-        <v>204</v>
+        <v>155</v>
+      </c>
+      <c r="B161" s="12">
+        <v>13703</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="B162" s="13">
-        <v>11800</v>
+        <v>156</v>
+      </c>
+      <c r="B162" s="12">
+        <v>761</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="B163" s="13">
-        <v>4057</v>
+        <v>157</v>
+      </c>
+      <c r="B163" s="12">
+        <v>140</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="B164" s="13">
-        <v>4920</v>
+        <v>158</v>
+      </c>
+      <c r="B164" s="12">
+        <v>180</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="B165" s="13">
-        <v>2274</v>
+        <v>159</v>
+      </c>
+      <c r="B165" s="12">
+        <v>189</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B166" s="13">
-        <v>3600</v>
+        <v>160</v>
+      </c>
+      <c r="B166" s="12">
+        <v>252</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="B167" s="13">
-        <v>1408</v>
+        <v>161</v>
+      </c>
+      <c r="B167" s="12">
+        <v>3632</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="B168" s="13">
-        <v>82</v>
+        <v>162</v>
+      </c>
+      <c r="B168" s="12">
+        <v>546</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="B169" s="13">
-        <v>718</v>
+        <v>163</v>
+      </c>
+      <c r="B169" s="12">
+        <v>700</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="B170" s="13">
-        <v>5036</v>
+        <v>164</v>
+      </c>
+      <c r="B170" s="12">
+        <v>1063</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="B171" s="13">
-        <v>838</v>
+        <v>165</v>
+      </c>
+      <c r="B171" s="12">
+        <v>1323</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="B172" s="13">
-        <v>361</v>
+        <v>166</v>
+      </c>
+      <c r="B172" s="12">
+        <v>7188</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="B173" s="13">
-        <v>374</v>
+        <v>167</v>
+      </c>
+      <c r="B173" s="12">
+        <v>1633</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="B174" s="13">
-        <v>390</v>
+        <v>168</v>
+      </c>
+      <c r="B174" s="12">
+        <v>2188</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="B175" s="13">
-        <v>375</v>
+        <v>169</v>
+      </c>
+      <c r="B175" s="12">
+        <v>3367</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="B176" s="13">
-        <v>412</v>
+        <v>170</v>
+      </c>
+      <c r="B176" s="12">
+        <v>77</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="B177" s="13">
-        <v>4385</v>
+        <v>171</v>
+      </c>
+      <c r="B177" s="12">
+        <v>10</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="B178" s="13">
-        <v>2389</v>
+        <v>172</v>
+      </c>
+      <c r="B178" s="12">
+        <v>18</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="B179" s="13">
-        <v>2608</v>
+        <v>173</v>
+      </c>
+      <c r="B179" s="12">
+        <v>28</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B180" s="13">
-        <v>2822</v>
+        <v>174</v>
+      </c>
+      <c r="B180" s="12">
+        <v>21</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="B181" s="13">
-        <v>2909</v>
+        <v>175</v>
+      </c>
+      <c r="B181" s="12">
+        <v>1827</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="B182" s="13">
-        <v>8493</v>
+        <v>176</v>
+      </c>
+      <c r="B182" s="12">
+        <v>480</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="B183" s="13">
-        <v>7057</v>
+        <v>177</v>
+      </c>
+      <c r="B183" s="12">
+        <v>671</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="B184" s="13">
-        <v>5026</v>
+        <v>178</v>
+      </c>
+      <c r="B184" s="12">
+        <v>676</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="B185" s="13">
-        <v>5431</v>
+        <v>179</v>
+      </c>
+      <c r="B185" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="B186" s="13">
-        <v>4903</v>
+        <v>180</v>
+      </c>
+      <c r="B186" s="12">
+        <v>218</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="B187" s="13">
-        <v>0</v>
+        <v>181</v>
+      </c>
+      <c r="B187" s="12">
+        <v>99</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="B188" s="13">
-        <v>3541</v>
+        <v>182</v>
+      </c>
+      <c r="B188" s="12">
+        <v>83</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="B189" s="13">
-        <v>2265</v>
+        <v>183</v>
+      </c>
+      <c r="B189" s="12">
+        <v>36</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="B190" s="13">
-        <v>2041</v>
+        <v>184</v>
+      </c>
+      <c r="B190" s="12">
+        <v>12542</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="B191" s="13">
-        <v>1976</v>
+        <v>185</v>
+      </c>
+      <c r="B191" s="12">
+        <v>367</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="B192" s="13">
-        <v>0</v>
+        <v>186</v>
+      </c>
+      <c r="B192" s="12">
+        <v>50626</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="B193" s="13">
-        <v>94</v>
+        <v>187</v>
+      </c>
+      <c r="B193" s="12">
+        <v>595</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="B194" s="13">
-        <v>0</v>
+        <v>188</v>
+      </c>
+      <c r="B194" s="12">
+        <v>111924</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="B195" s="13">
-        <v>94</v>
+        <v>189</v>
+      </c>
+      <c r="B195" s="12">
+        <v>18756</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="B196" s="13">
-        <v>0</v>
+        <v>190</v>
+      </c>
+      <c r="B196" s="12">
+        <v>132</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="B197" s="13">
-        <v>0</v>
+        <v>191</v>
+      </c>
+      <c r="B197" s="12">
+        <v>90604</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="B198" s="13">
-        <v>2454</v>
+        <v>192</v>
+      </c>
+      <c r="B198" s="12">
+        <v>91794</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="B199" s="13">
-        <v>162</v>
+        <v>193</v>
+      </c>
+      <c r="B199" s="12">
+        <v>2</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="B200" s="13">
-        <v>132</v>
+        <v>194</v>
+      </c>
+      <c r="B200" s="12">
+        <v>170742</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="B201" s="13">
-        <v>128</v>
+        <v>195</v>
+      </c>
+      <c r="B201" s="12">
+        <v>11732</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="B202" s="13">
-        <v>142</v>
+        <v>196</v>
+      </c>
+      <c r="B202" s="12">
+        <v>69755</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="B203" s="13">
-        <v>154</v>
+        <v>197</v>
+      </c>
+      <c r="B203" s="12">
+        <v>48374</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="B204" s="13">
-        <v>1014</v>
+        <v>198</v>
+      </c>
+      <c r="B204" s="12">
+        <v>14953</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="B205" s="13">
-        <v>731</v>
+        <v>199</v>
+      </c>
+      <c r="B205" s="12">
+        <v>167</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="B206" s="13">
-        <v>807</v>
+        <v>200</v>
+      </c>
+      <c r="B206" s="12">
+        <v>6261</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="B207" s="13">
-        <v>918</v>
+        <v>201</v>
+      </c>
+      <c r="B207" s="12">
+        <v>112521</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B208" s="13">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+      <c r="B208" s="12">
+        <v>51449</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="B209" s="13">
-        <v>1790</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+        <v>203</v>
+      </c>
+      <c r="B209" s="12">
+        <v>48238</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="B210" s="13">
-        <v>1204</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+      <c r="B210" s="12">
+        <v>12973</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="B211" s="13">
-        <v>1172</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+      <c r="B211" s="12">
+        <v>6193</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="B212" s="13">
-        <v>1411</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+        <v>206</v>
+      </c>
+      <c r="B212" s="12">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="B213" s="13">
+        <v>207</v>
+      </c>
+      <c r="B213" s="12">
+        <v>4313</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A214" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="B214" s="12">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A215" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="B215" s="12">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A216" s="9" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A214" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="B214" s="13">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A215" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="B215" s="13">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A216" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="B216" s="13">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A217" s="9" t="s">
+      <c r="B216" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A217" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="B217" s="13">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B217" s="22">
+        <v>12916</v>
+      </c>
+      <c r="C217" s="19"/>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="B218" s="13">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B218" s="12">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B219" s="13">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B219" s="12">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="B220" s="13">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B220" s="12">
+        <v>12011</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="B221" s="13">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B221" s="12">
+        <v>4138</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="B222" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B222" s="12">
+        <v>5034</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="B223" s="13">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B223" s="12">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="B224" s="13">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B224" s="12">
+        <v>3666</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="B225" s="13">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B225" s="12">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="B226" s="13">
+      <c r="B226" s="12">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A227" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="B227" s="12">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A228" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="B228" s="12">
+        <v>5093</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A229" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B229" s="12">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A230" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="B230" s="12">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A231" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="B231" s="12">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A232" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="B232" s="12">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A233" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="B233" s="12">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A234" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="B234" s="12">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A235" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B235" s="12">
+        <v>4434</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A236" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B236" s="12">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A237" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B237" s="12">
+        <v>2639</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A238" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="B238" s="12">
+        <v>2837</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A239" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B239" s="12">
+        <v>2948</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A240" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="B240" s="12">
+        <v>8669</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A241" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="B241" s="12">
+        <v>7225</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A242" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B242" s="12">
+        <v>5123</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A243" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="B243" s="12">
+        <v>5548</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A244" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="B244" s="12">
+        <v>4998</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A245" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="B245" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A246" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="B246" s="12">
+        <v>3605</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A247" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="B247" s="12">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A248" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="B248" s="12">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A249" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="B249" s="12">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A250" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="B250" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A251" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="B251" s="12">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A252" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="B252" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A253" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="B253" s="12">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A254" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B254" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A255" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="B255" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A256" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="B256" s="12">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A257" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="B257" s="12">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A258" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="B258" s="12">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A259" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="B259" s="12">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A260" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="B260" s="12">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A261" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="B261" s="12">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A262" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B262" s="12">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A263" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="B263" s="12">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A264" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="B264" s="12">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A265" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="B265" s="12">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A266" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="B266" s="12">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A267" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B267" s="12">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A268" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="B268" s="12">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A269" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B269" s="12">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A270" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="B270" s="12">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A271" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="B271" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A272" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="B272" s="12">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A273" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B273" s="12">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A274" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="B274" s="12">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A275" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="B275" s="12">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A276" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="B276" s="12">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A277" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="B277" s="12">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A278" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="B278" s="12">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A279" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="B279" s="12">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A280" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="B280" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A281" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="B281" s="12">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A282" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="B282" s="12">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A283" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="B283" s="12">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A284" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="B284" s="12">
         <v>12</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A227" s="1"/>
-      <c r="B227" s="14"/>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A228" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="B228" s="14"/>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A229" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="B229" s="14"/>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A230" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B230" s="14"/>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A231" s="10"/>
-      <c r="B231" s="15"/>
-      <c r="C231" s="11"/>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A285" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="B285" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A286" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="B286" s="12">
+        <v>5677</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A287" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="B287" s="12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A288" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="B288" s="12">
+        <v>4652</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A289" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="B289" s="12">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A290" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="B290" s="12">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A291" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="B291" s="12">
+        <v>7574</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A292" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="B292" s="12">
+        <v>4436</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A293" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="B293" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A294" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="B294" s="12">
+        <v>11031</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A295" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="B295" s="12">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A296" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="B296" s="12">
+        <v>5619</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A297" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B297" s="12">
+        <v>3666</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A298" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="B298" s="12">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A299" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="B299" s="12">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A300" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="B300" s="12">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A301" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="B301" s="12">
+        <v>8478</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A302" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="B302" s="12">
+        <v>4138</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A303" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="B303" s="12">
+        <v>5034</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A304" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="B304" s="12">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A305" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="B305" s="12">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A306" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="B306" s="12">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A307" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="B307" s="12">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A308" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="B308" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A309" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="B309" s="12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A310" s="1"/>
+      <c r="B310" s="13"/>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A311" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B311" s="13"/>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A312" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B312" s="13"/>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A313" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B313" s="13"/>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A314" s="10"/>
+      <c r="B314" s="14"/>
+      <c r="C314" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:B5" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/dados/dados.xlsx
+++ b/dados/dados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\04 - Relatórios\Relatórios ROTINA\02 - Relatórios\2026\06 - Junho\ROTINA 2026_06_01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\04 - Relatórios\Relatórios ROTINA\02 - Relatórios\2026\06 - Junho\ROTINA 2026_06_22\Formatados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF77DB73-6196-44A4-925E-C8299DCD4D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{255C5465-FC7C-4FD4-9210-8C3E4D1945EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
     <t>1. QUANTIDADE DE ESCOLAS NA REDE</t>
   </si>
   <si>
-    <t>1.1. QUANTIDADE DE ESCOLAS COM MATRÍCULA ATIVA EM 01/06/2026</t>
+    <t>1.1. QUANTIDADE DE ESCOLAS COM MATRÍCULA ATIVA EM 22/06/2026</t>
   </si>
   <si>
     <t>1.1.1. Quantidade de escolas com oferta de Ensino Fundamental</t>
@@ -590,9 +590,6 @@
     <t>4.7.6.3. Quantidade de alunos na 3ª Etapa do Curso técnico integrado na modalidade EJA</t>
   </si>
   <si>
-    <t>4.8 Quantidade de alunos público-alvo da Educação Especial (alunos com deficiência)</t>
-  </si>
-  <si>
     <t>4.9 Quantidade de alunos com raça/cor declarada - Amarela</t>
   </si>
   <si>
@@ -953,10 +950,13 @@
     <t>FONTE: SEGES</t>
   </si>
   <si>
-    <t>DATA: 01/06/2026</t>
+    <t>DATA: 22/06/2026</t>
   </si>
   <si>
     <t>GEI/SEE/EAARAÚJO</t>
+  </si>
+  <si>
+    <t>4.8 Quantidade de alunos público-alvo do Atendimento Educacional Especializado - AEE (alunos com deficiência)</t>
   </si>
 </sst>
 </file>
@@ -965,7 +965,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -1114,7 +1114,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1138,20 +1138,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1190,7 +1189,7 @@
         <xdr:cNvPr id="3" name="Imagem 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9441767F-3C14-2DD1-3E51-46F1327EFB43}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{996C27DB-C451-739D-0F60-523EB2911BD7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1501,8 +1500,8 @@
   <dimension ref="A1:C314"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="16.5" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="109.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="112.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" style="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3.7109375" style="1" customWidth="1"/>
     <col min="4" max="16384" width="11.42578125" style="8" hidden="1"/>
   </cols>
@@ -1510,10 +1509,10 @@
     <row r="1" spans="1:3" s="1" customFormat="1" ht="82.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:3" s="1" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:3" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="B3" s="16"/>
+      <c r="A3" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="B3" s="15"/>
       <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1526,29 +1525,29 @@
       </c>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
+    <row r="6" spans="1:3" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="17">
         <v>384</v>
       </c>
-      <c r="C6" s="19"/>
-    </row>
-    <row r="7" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
+      <c r="C6" s="18"/>
+    </row>
+    <row r="7" spans="1:3" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="21">
         <v>383</v>
       </c>
-      <c r="C7" s="19"/>
+      <c r="C7" s="18"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <v>267</v>
       </c>
     </row>
@@ -1556,7 +1555,7 @@
       <c r="A9" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <v>98</v>
       </c>
     </row>
@@ -1564,7 +1563,7 @@
       <c r="A10" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <v>235</v>
       </c>
     </row>
@@ -1572,7 +1571,7 @@
       <c r="A11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>288</v>
       </c>
     </row>
@@ -1580,7 +1579,7 @@
       <c r="A12" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <v>280</v>
       </c>
     </row>
@@ -1588,7 +1587,7 @@
       <c r="A13" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <v>148</v>
       </c>
     </row>
@@ -1596,7 +1595,7 @@
       <c r="A14" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="11">
         <v>18</v>
       </c>
     </row>
@@ -1604,7 +1603,7 @@
       <c r="A15" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="11">
         <v>171</v>
       </c>
     </row>
@@ -1612,7 +1611,7 @@
       <c r="A16" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="11">
         <v>26</v>
       </c>
     </row>
@@ -1620,7 +1619,7 @@
       <c r="A17" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <v>94</v>
       </c>
     </row>
@@ -1628,7 +1627,7 @@
       <c r="A18" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <v>139</v>
       </c>
     </row>
@@ -1636,7 +1635,7 @@
       <c r="A19" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="11">
         <v>2</v>
       </c>
     </row>
@@ -1644,7 +1643,7 @@
       <c r="A20" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="11">
         <v>35</v>
       </c>
     </row>
@@ -1652,7 +1651,7 @@
       <c r="A21" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="11">
         <v>6</v>
       </c>
     </row>
@@ -1660,23 +1659,23 @@
       <c r="A22" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="12">
-        <v>306</v>
+      <c r="B22" s="11">
+        <v>307</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="12">
-        <v>77</v>
+      <c r="B23" s="11">
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="11">
         <v>234</v>
       </c>
     </row>
@@ -1684,7 +1683,7 @@
       <c r="A25" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="11">
         <v>154</v>
       </c>
     </row>
@@ -1692,7 +1691,7 @@
       <c r="A26" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="11">
         <v>53</v>
       </c>
     </row>
@@ -1700,7 +1699,7 @@
       <c r="A27" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="11">
         <v>5</v>
       </c>
     </row>
@@ -1708,7 +1707,7 @@
       <c r="A28" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="11">
         <v>40</v>
       </c>
     </row>
@@ -1716,7 +1715,7 @@
       <c r="A29" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="11">
         <v>355</v>
       </c>
     </row>
@@ -1724,23 +1723,23 @@
       <c r="A30" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="12">
-        <v>221</v>
+      <c r="B30" s="11">
+        <v>220</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="12">
-        <v>233</v>
+      <c r="B31" s="11">
+        <v>232</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="11">
         <v>168</v>
       </c>
     </row>
@@ -1748,7 +1747,7 @@
       <c r="A33" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="11">
         <v>37</v>
       </c>
     </row>
@@ -1756,7 +1755,7 @@
       <c r="A34" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B34" s="12">
+      <c r="B34" s="11">
         <v>25</v>
       </c>
     </row>
@@ -1764,7 +1763,7 @@
       <c r="A35" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="11">
         <v>10</v>
       </c>
     </row>
@@ -1772,7 +1771,7 @@
       <c r="A36" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B36" s="12">
+      <c r="B36" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1780,7 +1779,7 @@
       <c r="A37" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B37" s="12">
+      <c r="B37" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1788,80 +1787,80 @@
       <c r="A38" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="21" t="s">
+    <row r="39" spans="1:3" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="B39" s="22">
-        <v>14664</v>
-      </c>
-      <c r="C39" s="19"/>
+      <c r="B39" s="21">
+        <v>14860</v>
+      </c>
+      <c r="C39" s="18"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="12">
-        <v>6773</v>
+      <c r="B40" s="11">
+        <v>6944</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="12">
-        <v>712</v>
+      <c r="B41" s="11">
+        <v>754</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B42" s="12">
-        <v>7179</v>
+      <c r="B42" s="11">
+        <v>7162</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="12">
-        <v>2518</v>
+      <c r="B43" s="11">
+        <v>2523</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="12">
-        <v>644</v>
+      <c r="B44" s="11">
+        <v>648</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B45" s="12">
-        <v>124</v>
+      <c r="B45" s="11">
+        <v>125</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B46" s="12">
-        <v>131</v>
+      <c r="B46" s="11">
+        <v>132</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="12">
+      <c r="B47" s="11">
         <v>131</v>
       </c>
     </row>
@@ -1869,7 +1868,7 @@
       <c r="A48" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="12">
+      <c r="B48" s="11">
         <v>124</v>
       </c>
     </row>
@@ -1877,31 +1876,31 @@
       <c r="A49" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B49" s="12">
-        <v>134</v>
+      <c r="B49" s="11">
+        <v>136</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B50" s="12">
-        <v>1874</v>
+      <c r="B50" s="11">
+        <v>1875</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="12">
-        <v>446</v>
+      <c r="B51" s="11">
+        <v>447</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B52" s="12">
+      <c r="B52" s="11">
         <v>453</v>
       </c>
     </row>
@@ -1909,55 +1908,55 @@
       <c r="A53" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="12">
-        <v>461</v>
+      <c r="B53" s="11">
+        <v>460</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B54" s="12">
-        <v>514</v>
+      <c r="B54" s="11">
+        <v>515</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B55" s="12">
-        <v>3465</v>
+      <c r="B55" s="11">
+        <v>3463</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B56" s="12">
-        <v>2626</v>
+      <c r="B56" s="11">
+        <v>2625</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B57" s="12">
-        <v>942</v>
+      <c r="B57" s="11">
+        <v>943</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B58" s="12">
-        <v>886</v>
+      <c r="B58" s="11">
+        <v>884</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B59" s="12">
+      <c r="B59" s="11">
         <v>798</v>
       </c>
     </row>
@@ -1965,7 +1964,7 @@
       <c r="A60" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B60" s="12">
+      <c r="B60" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1973,15 +1972,15 @@
       <c r="A61" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B61" s="12">
-        <v>839</v>
+      <c r="B61" s="11">
+        <v>838</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B62" s="12">
+      <c r="B62" s="11">
         <v>286</v>
       </c>
     </row>
@@ -1989,15 +1988,15 @@
       <c r="A63" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B63" s="12">
-        <v>279</v>
+      <c r="B63" s="11">
+        <v>278</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B64" s="12">
+      <c r="B64" s="11">
         <v>274</v>
       </c>
     </row>
@@ -2005,7 +2004,7 @@
       <c r="A65" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B65" s="12">
+      <c r="B65" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2013,7 +2012,7 @@
       <c r="A66" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B66" s="12">
+      <c r="B66" s="11">
         <v>18</v>
       </c>
     </row>
@@ -2021,7 +2020,7 @@
       <c r="A67" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B67" s="12">
+      <c r="B67" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2029,7 +2028,7 @@
       <c r="A68" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B68" s="12">
+      <c r="B68" s="11">
         <v>18</v>
       </c>
     </row>
@@ -2037,7 +2036,7 @@
       <c r="A69" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B69" s="12">
+      <c r="B69" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2045,7 +2044,7 @@
       <c r="A70" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B70" s="12">
+      <c r="B70" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2053,31 +2052,31 @@
       <c r="A71" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B71" s="12">
-        <v>1178</v>
+      <c r="B71" s="11">
+        <v>1158</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B72" s="12">
-        <v>177</v>
+      <c r="B72" s="11">
+        <v>172</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B73" s="12">
-        <v>41</v>
+      <c r="B73" s="11">
+        <v>39</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="B74" s="12">
+      <c r="B74" s="11">
         <v>45</v>
       </c>
     </row>
@@ -2085,95 +2084,95 @@
       <c r="A75" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B75" s="12">
-        <v>43</v>
+      <c r="B75" s="11">
+        <v>42</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B76" s="12">
-        <v>48</v>
+      <c r="B76" s="11">
+        <v>46</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B77" s="12">
-        <v>449</v>
+      <c r="B77" s="11">
+        <v>438</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B78" s="12">
-        <v>96</v>
+      <c r="B78" s="11">
+        <v>93</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B79" s="12">
-        <v>107</v>
+      <c r="B79" s="11">
+        <v>104</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B80" s="12">
-        <v>121</v>
+      <c r="B80" s="11">
+        <v>120</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B81" s="12">
-        <v>125</v>
+      <c r="B81" s="11">
+        <v>121</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B82" s="12">
-        <v>434</v>
+      <c r="B82" s="11">
+        <v>430</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B83" s="12">
-        <v>134</v>
+      <c r="B83" s="11">
+        <v>133</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B84" s="12">
-        <v>137</v>
+      <c r="B84" s="11">
+        <v>136</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B85" s="12">
-        <v>163</v>
+      <c r="B85" s="11">
+        <v>161</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B86" s="12">
+      <c r="B86" s="11">
         <v>8</v>
       </c>
     </row>
@@ -2181,7 +2180,7 @@
       <c r="A87" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B87" s="12">
+      <c r="B87" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2189,7 +2188,7 @@
       <c r="A88" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B88" s="12">
+      <c r="B88" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2197,7 +2196,7 @@
       <c r="A89" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B89" s="12">
+      <c r="B89" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2205,7 +2204,7 @@
       <c r="A90" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B90" s="12">
+      <c r="B90" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2213,7 +2212,7 @@
       <c r="A91" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B91" s="12">
+      <c r="B91" s="11">
         <v>99</v>
       </c>
     </row>
@@ -2221,7 +2220,7 @@
       <c r="A92" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="B92" s="12">
+      <c r="B92" s="11">
         <v>30</v>
       </c>
     </row>
@@ -2229,7 +2228,7 @@
       <c r="A93" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B93" s="12">
+      <c r="B93" s="11">
         <v>34</v>
       </c>
     </row>
@@ -2237,7 +2236,7 @@
       <c r="A94" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B94" s="12">
+      <c r="B94" s="11">
         <v>35</v>
       </c>
     </row>
@@ -2245,7 +2244,7 @@
       <c r="A95" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B95" s="12">
+      <c r="B95" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2253,7 +2252,7 @@
       <c r="A96" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B96" s="12">
+      <c r="B96" s="11">
         <v>11</v>
       </c>
     </row>
@@ -2261,7 +2260,7 @@
       <c r="A97" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B97" s="12">
+      <c r="B97" s="11">
         <v>4</v>
       </c>
     </row>
@@ -2269,7 +2268,7 @@
       <c r="A98" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="12">
+      <c r="B98" s="11">
         <v>5</v>
       </c>
     </row>
@@ -2277,7 +2276,7 @@
       <c r="A99" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B99" s="12">
+      <c r="B99" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2285,47 +2284,47 @@
       <c r="A100" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B100" s="12">
-        <v>13328</v>
+      <c r="B100" s="11">
+        <v>13538</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B101" s="12">
-        <v>1336</v>
+      <c r="B101" s="11">
+        <v>1322</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B102" s="12">
-        <v>2397</v>
+      <c r="B102" s="11">
+        <v>2394</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B103" s="12">
-        <v>1639</v>
+      <c r="B103" s="11">
+        <v>1637</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B104" s="12">
-        <v>485</v>
+      <c r="B104" s="11">
+        <v>484</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="B105" s="12">
+      <c r="B105" s="11">
         <v>8</v>
       </c>
     </row>
@@ -2333,7 +2332,7 @@
       <c r="A106" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="B106" s="12">
+      <c r="B106" s="11">
         <v>265</v>
       </c>
     </row>
@@ -2341,71 +2340,71 @@
       <c r="A107" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B107" s="12">
-        <v>4782</v>
+      <c r="B107" s="11">
+        <v>4768</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B108" s="12">
-        <v>1959</v>
+      <c r="B108" s="11">
+        <v>1955</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="B109" s="12">
-        <v>1932</v>
+      <c r="B109" s="11">
+        <v>1930</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="B110" s="12">
-        <v>891</v>
+      <c r="B110" s="11">
+        <v>883</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B111" s="12">
-        <v>642</v>
+      <c r="B111" s="11">
+        <v>639</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B112" s="12">
-        <v>297</v>
+      <c r="B112" s="11">
+        <v>295</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B113" s="12">
-        <v>284</v>
+      <c r="B113" s="11">
+        <v>285</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="B114" s="12">
-        <v>50</v>
+      <c r="B114" s="11">
+        <v>48</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B115" s="12">
+      <c r="B115" s="11">
         <v>11</v>
       </c>
     </row>
@@ -2413,281 +2412,281 @@
       <c r="A116" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B116" s="12" t="s">
+      <c r="B116" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="117" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="21" t="s">
+    <row r="117" spans="1:3" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="B117" s="22">
-        <v>216285</v>
-      </c>
-      <c r="C117" s="19"/>
+      <c r="B117" s="21">
+        <v>216936</v>
+      </c>
+      <c r="C117" s="18"/>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B118" s="12">
-        <v>182415</v>
+      <c r="B118" s="11">
+        <v>182019</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="B119" s="12">
-        <v>18299</v>
+      <c r="B119" s="11">
+        <v>18875</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="B120" s="12">
-        <v>15571</v>
+      <c r="B120" s="11">
+        <v>16042</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B121" s="12" t="s">
+      <c r="B121" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="122" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="21" t="s">
+    <row r="122" spans="1:3" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="B122" s="22">
-        <v>182400</v>
-      </c>
-      <c r="C122" s="19"/>
+      <c r="B122" s="21">
+        <v>181924</v>
+      </c>
+      <c r="C122" s="18"/>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="B123" s="12">
-        <v>10350</v>
+      <c r="B123" s="11">
+        <v>10624</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B124" s="12">
-        <v>14360</v>
+      <c r="B124" s="11">
+        <v>14832</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B125" s="12">
-        <v>182057</v>
+      <c r="B125" s="11">
+        <v>181665</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B126" s="12">
-        <v>51449</v>
+      <c r="B126" s="11">
+        <v>51355</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B127" s="12">
-        <v>48238</v>
+      <c r="B127" s="11">
+        <v>48168</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B128" s="12">
-        <v>12973</v>
+      <c r="B128" s="11">
+        <v>12909</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B129" s="12">
-        <v>48374</v>
+      <c r="B129" s="11">
+        <v>48290</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B130" s="12">
-        <v>14953</v>
+      <c r="B130" s="11">
+        <v>14886</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B131" s="12">
-        <v>167</v>
+      <c r="B131" s="11">
+        <v>168</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B132" s="12">
-        <v>6261</v>
+      <c r="B132" s="11">
+        <v>6243</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B133" s="12">
-        <v>63154</v>
+      <c r="B133" s="11">
+        <v>63148</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B134" s="12">
-        <v>10858</v>
+      <c r="B134" s="11">
+        <v>10861</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B135" s="12">
-        <v>1938</v>
+      <c r="B135" s="11">
+        <v>1942</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="B136" s="12">
-        <v>2157</v>
+      <c r="B136" s="11">
+        <v>2164</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="B137" s="12">
-        <v>2142</v>
+      <c r="B137" s="11">
+        <v>2136</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B138" s="12">
-        <v>2132</v>
+      <c r="B138" s="11">
+        <v>2122</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B139" s="12">
-        <v>2489</v>
+      <c r="B139" s="11">
+        <v>2497</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B140" s="12">
-        <v>52296</v>
+      <c r="B140" s="11">
+        <v>52287</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="B141" s="12">
-        <v>12278</v>
+      <c r="B141" s="11">
+        <v>12277</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B142" s="12">
-        <v>12492</v>
+      <c r="B142" s="11">
+        <v>12503</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="B143" s="12">
-        <v>13115</v>
+      <c r="B143" s="11">
+        <v>13110</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="B144" s="12">
-        <v>14411</v>
+      <c r="B144" s="11">
+        <v>14397</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="B145" s="12">
-        <v>105190</v>
+      <c r="B145" s="11">
+        <v>104989</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B146" s="12">
-        <v>80151</v>
+      <c r="B146" s="11">
+        <v>80100</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B147" s="12">
-        <v>29938</v>
+      <c r="B147" s="11">
+        <v>30009</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B148" s="12">
-        <v>27555</v>
+      <c r="B148" s="11">
+        <v>27578</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="B149" s="12">
-        <v>22658</v>
+      <c r="B149" s="11">
+        <v>22513</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="B150" s="12">
+      <c r="B150" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2695,39 +2694,39 @@
       <c r="A151" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="B151" s="12">
-        <v>25039</v>
+      <c r="B151" s="11">
+        <v>24889</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="B152" s="12">
-        <v>9871</v>
+      <c r="B152" s="11">
+        <v>9835</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B153" s="12">
-        <v>8018</v>
+      <c r="B153" s="11">
+        <v>7939</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="B154" s="12">
-        <v>7150</v>
+      <c r="B154" s="11">
+        <v>7115</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="B155" s="12">
+      <c r="B155" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2735,15 +2734,15 @@
       <c r="A156" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="B156" s="12">
-        <v>368</v>
+      <c r="B156" s="11">
+        <v>361</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="B157" s="12">
+      <c r="B157" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2751,15 +2750,15 @@
       <c r="A158" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="B158" s="12">
-        <v>368</v>
+      <c r="B158" s="11">
+        <v>361</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="B159" s="12">
+      <c r="B159" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2767,7 +2766,7 @@
       <c r="A160" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="B160" s="12">
+      <c r="B160" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2775,199 +2774,199 @@
       <c r="A161" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B161" s="12">
-        <v>13703</v>
+      <c r="B161" s="11">
+        <v>13521</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="B162" s="12">
-        <v>761</v>
+      <c r="B162" s="11">
+        <v>752</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="B163" s="12">
-        <v>140</v>
+      <c r="B163" s="11">
+        <v>144</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="B164" s="12">
-        <v>180</v>
+      <c r="B164" s="11">
+        <v>178</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="B165" s="12">
-        <v>189</v>
+      <c r="B165" s="11">
+        <v>186</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="B166" s="12">
-        <v>252</v>
+      <c r="B166" s="11">
+        <v>244</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="B167" s="12">
-        <v>3632</v>
+      <c r="B167" s="11">
+        <v>3545</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="B168" s="12">
-        <v>546</v>
+      <c r="B168" s="11">
+        <v>525</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="B169" s="12">
-        <v>700</v>
+      <c r="B169" s="11">
+        <v>675</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="B170" s="12">
-        <v>1063</v>
+      <c r="B170" s="11">
+        <v>1056</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="B171" s="12">
-        <v>1323</v>
+      <c r="B171" s="11">
+        <v>1289</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="B172" s="12">
-        <v>7188</v>
+      <c r="B172" s="11">
+        <v>7174</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="B173" s="12">
-        <v>1633</v>
+      <c r="B173" s="11">
+        <v>1592</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="B174" s="12">
-        <v>2188</v>
+      <c r="B174" s="11">
+        <v>2139</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B175" s="12">
-        <v>3367</v>
+      <c r="B175" s="11">
+        <v>3443</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="B176" s="12">
-        <v>77</v>
+      <c r="B176" s="11">
+        <v>85</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="B177" s="12">
-        <v>10</v>
+      <c r="B177" s="11">
+        <v>11</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B178" s="12">
-        <v>18</v>
+      <c r="B178" s="11">
+        <v>21</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B179" s="12">
-        <v>28</v>
+      <c r="B179" s="11">
+        <v>31</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B180" s="12">
-        <v>21</v>
+      <c r="B180" s="11">
+        <v>22</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="B181" s="12">
-        <v>1827</v>
+      <c r="B181" s="11">
+        <v>1746</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="B182" s="12">
-        <v>480</v>
+      <c r="B182" s="11">
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="B183" s="12">
-        <v>671</v>
+      <c r="B183" s="11">
+        <v>646</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="B184" s="12">
-        <v>676</v>
+      <c r="B184" s="11">
+        <v>654</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="B185" s="12">
+      <c r="B185" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2975,23 +2974,23 @@
       <c r="A186" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B186" s="12">
-        <v>218</v>
+      <c r="B186" s="11">
+        <v>219</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="B187" s="12">
-        <v>99</v>
+      <c r="B187" s="11">
+        <v>100</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B188" s="12">
+      <c r="B188" s="11">
         <v>83</v>
       </c>
     </row>
@@ -2999,997 +2998,996 @@
       <c r="A189" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="B189" s="12">
+      <c r="B189" s="11">
         <v>36</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="B190" s="12">
-        <v>12542</v>
+        <v>306</v>
+      </c>
+      <c r="B190" s="11">
+        <v>12683</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="B191" s="12">
-        <v>367</v>
+        <v>184</v>
+      </c>
+      <c r="B191" s="11">
+        <v>359</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="B192" s="12">
-        <v>50626</v>
+        <v>185</v>
+      </c>
+      <c r="B192" s="11">
+        <v>50539</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="B193" s="12">
-        <v>595</v>
+        <v>186</v>
+      </c>
+      <c r="B193" s="11">
+        <v>590</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="B194" s="12">
-        <v>111924</v>
+        <v>187</v>
+      </c>
+      <c r="B194" s="11">
+        <v>111647</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="B195" s="12">
-        <v>18756</v>
+        <v>188</v>
+      </c>
+      <c r="B195" s="11">
+        <v>18718</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="B196" s="12">
-        <v>132</v>
+        <v>189</v>
+      </c>
+      <c r="B196" s="11">
+        <v>71</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="B197" s="12">
-        <v>90604</v>
+        <v>190</v>
+      </c>
+      <c r="B197" s="11">
+        <v>90445</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="B198" s="12">
-        <v>91794</v>
+        <v>191</v>
+      </c>
+      <c r="B198" s="11">
+        <v>91477</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="B199" s="12">
+        <v>192</v>
+      </c>
+      <c r="B199" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="B200" s="12">
-        <v>170742</v>
+        <v>193</v>
+      </c>
+      <c r="B200" s="11">
+        <v>170606</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="B201" s="12">
-        <v>11732</v>
+        <v>194</v>
+      </c>
+      <c r="B201" s="11">
+        <v>11387</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="B202" s="12">
-        <v>69755</v>
+        <v>195</v>
+      </c>
+      <c r="B202" s="11">
+        <v>69587</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="B203" s="12">
-        <v>48374</v>
+        <v>196</v>
+      </c>
+      <c r="B203" s="11">
+        <v>48290</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="B204" s="12">
-        <v>14953</v>
+        <v>197</v>
+      </c>
+      <c r="B204" s="11">
+        <v>14886</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="B205" s="12">
-        <v>167</v>
+        <v>198</v>
+      </c>
+      <c r="B205" s="11">
+        <v>168</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="B206" s="12">
-        <v>6261</v>
+        <v>199</v>
+      </c>
+      <c r="B206" s="11">
+        <v>6243</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B207" s="12">
-        <v>112521</v>
+        <v>200</v>
+      </c>
+      <c r="B207" s="11">
+        <v>112294</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="B208" s="12">
-        <v>51449</v>
+        <v>201</v>
+      </c>
+      <c r="B208" s="11">
+        <v>51355</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="B209" s="12">
-        <v>48238</v>
+        <v>202</v>
+      </c>
+      <c r="B209" s="11">
+        <v>48168</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="B210" s="12">
-        <v>12973</v>
+        <v>203</v>
+      </c>
+      <c r="B210" s="11">
+        <v>12909</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="B211" s="12">
-        <v>6193</v>
+        <v>204</v>
+      </c>
+      <c r="B211" s="11">
+        <v>6157</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="B212" s="12">
-        <v>1425</v>
+        <v>205</v>
+      </c>
+      <c r="B212" s="11">
+        <v>1403</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="B213" s="12">
-        <v>4313</v>
+        <v>206</v>
+      </c>
+      <c r="B213" s="11">
+        <v>4300</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="B214" s="12">
+        <v>207</v>
+      </c>
+      <c r="B214" s="11">
         <v>329</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="B215" s="12">
-        <v>126</v>
+        <v>208</v>
+      </c>
+      <c r="B215" s="11">
+        <v>125</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B216" s="12" t="s">
+      <c r="B216" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="217" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="21" t="s">
-        <v>210</v>
-      </c>
-      <c r="B217" s="22">
-        <v>12916</v>
-      </c>
-      <c r="C217" s="19"/>
+    <row r="217" spans="1:3" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A217" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="B217" s="21">
+        <v>13072</v>
+      </c>
+      <c r="C217" s="18"/>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="B218" s="12">
-        <v>891</v>
+        <v>210</v>
+      </c>
+      <c r="B218" s="11">
+        <v>912</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="B219" s="12">
-        <v>251</v>
+        <v>211</v>
+      </c>
+      <c r="B219" s="11">
+        <v>265</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="B220" s="12">
-        <v>12011</v>
+        <v>212</v>
+      </c>
+      <c r="B220" s="11">
+        <v>12145</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="B221" s="12">
-        <v>4138</v>
+        <v>213</v>
+      </c>
+      <c r="B221" s="11">
+        <v>4179</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="B222" s="12">
-        <v>5034</v>
+        <v>214</v>
+      </c>
+      <c r="B222" s="11">
+        <v>5084</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="B223" s="12">
-        <v>2333</v>
+        <v>215</v>
+      </c>
+      <c r="B223" s="11">
+        <v>2381</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="B224" s="12">
-        <v>3666</v>
+        <v>216</v>
+      </c>
+      <c r="B224" s="11">
+        <v>3707</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="B225" s="12">
-        <v>1450</v>
+        <v>217</v>
+      </c>
+      <c r="B225" s="11">
+        <v>1470</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B226" s="12">
+        <v>218</v>
+      </c>
+      <c r="B226" s="11">
         <v>84</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="B227" s="12">
-        <v>717</v>
+        <v>219</v>
+      </c>
+      <c r="B227" s="11">
+        <v>723</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="B228" s="12">
-        <v>5093</v>
+        <v>220</v>
+      </c>
+      <c r="B228" s="11">
+        <v>5173</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="B229" s="12">
-        <v>856</v>
+        <v>221</v>
+      </c>
+      <c r="B229" s="11">
+        <v>876</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="B230" s="12">
-        <v>371</v>
+        <v>222</v>
+      </c>
+      <c r="B230" s="11">
+        <v>378</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="B231" s="12">
-        <v>386</v>
+        <v>223</v>
+      </c>
+      <c r="B231" s="11">
+        <v>393</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="B232" s="12">
-        <v>398</v>
+        <v>224</v>
+      </c>
+      <c r="B232" s="11">
+        <v>408</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="B233" s="12">
-        <v>386</v>
+        <v>225</v>
+      </c>
+      <c r="B233" s="11">
+        <v>396</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="B234" s="12">
-        <v>421</v>
+        <v>226</v>
+      </c>
+      <c r="B234" s="11">
+        <v>436</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="B235" s="12">
-        <v>4434</v>
+        <v>227</v>
+      </c>
+      <c r="B235" s="11">
+        <v>4497</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="B236" s="12">
-        <v>2429</v>
+        <v>228</v>
+      </c>
+      <c r="B236" s="11">
+        <v>2458</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="B237" s="12">
-        <v>2639</v>
+        <v>229</v>
+      </c>
+      <c r="B237" s="11">
+        <v>2661</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="B238" s="12">
-        <v>2837</v>
+        <v>230</v>
+      </c>
+      <c r="B238" s="11">
+        <v>2875</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="B239" s="12">
-        <v>2948</v>
+        <v>231</v>
+      </c>
+      <c r="B239" s="11">
+        <v>2968</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="B240" s="12">
-        <v>8669</v>
+        <v>232</v>
+      </c>
+      <c r="B240" s="11">
+        <v>8772</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="B241" s="12">
-        <v>7225</v>
+        <v>233</v>
+      </c>
+      <c r="B241" s="11">
+        <v>7306</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="B242" s="12">
-        <v>5123</v>
+        <v>234</v>
+      </c>
+      <c r="B242" s="11">
+        <v>5182</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="B243" s="12">
-        <v>5548</v>
+        <v>235</v>
+      </c>
+      <c r="B243" s="11">
+        <v>5594</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="B244" s="12">
-        <v>4998</v>
+        <v>236</v>
+      </c>
+      <c r="B244" s="11">
+        <v>5037</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="B245" s="12">
+        <v>237</v>
+      </c>
+      <c r="B245" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="B246" s="12">
-        <v>3605</v>
+        <v>238</v>
+      </c>
+      <c r="B246" s="11">
+        <v>3630</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="B247" s="12">
-        <v>2322</v>
+        <v>239</v>
+      </c>
+      <c r="B247" s="11">
+        <v>2351</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="B248" s="12">
-        <v>2049</v>
+        <v>240</v>
+      </c>
+      <c r="B248" s="11">
+        <v>2073</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="B249" s="12">
-        <v>2008</v>
+        <v>241</v>
+      </c>
+      <c r="B249" s="11">
+        <v>2032</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="B250" s="12">
+        <v>242</v>
+      </c>
+      <c r="B250" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="B251" s="12">
-        <v>94</v>
+        <v>243</v>
+      </c>
+      <c r="B251" s="11">
+        <v>95</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="B252" s="12">
+        <v>244</v>
+      </c>
+      <c r="B252" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="B253" s="12">
-        <v>94</v>
+        <v>245</v>
+      </c>
+      <c r="B253" s="11">
+        <v>95</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="B254" s="12">
+        <v>246</v>
+      </c>
+      <c r="B254" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="B255" s="12">
+        <v>247</v>
+      </c>
+      <c r="B255" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="B256" s="12">
-        <v>2511</v>
+        <v>248</v>
+      </c>
+      <c r="B256" s="11">
+        <v>2569</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="B257" s="12">
-        <v>163</v>
+        <v>249</v>
+      </c>
+      <c r="B257" s="11">
+        <v>167</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="B258" s="12">
-        <v>132</v>
+        <v>250</v>
+      </c>
+      <c r="B258" s="11">
+        <v>127</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="B259" s="12">
-        <v>135</v>
+        <v>251</v>
+      </c>
+      <c r="B259" s="11">
+        <v>131</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="B260" s="12">
-        <v>141</v>
+        <v>252</v>
+      </c>
+      <c r="B260" s="11">
+        <v>140</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="B261" s="12">
-        <v>152</v>
+        <v>253</v>
+      </c>
+      <c r="B261" s="11">
+        <v>147</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="B262" s="12">
-        <v>1035</v>
+        <v>254</v>
+      </c>
+      <c r="B262" s="11">
+        <v>1048</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="B263" s="12">
-        <v>729</v>
+        <v>255</v>
+      </c>
+      <c r="B263" s="11">
+        <v>690</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="B264" s="12">
-        <v>812</v>
+        <v>256</v>
+      </c>
+      <c r="B264" s="11">
+        <v>790</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="B265" s="12">
-        <v>927</v>
+        <v>257</v>
+      </c>
+      <c r="B265" s="11">
+        <v>928</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="B266" s="12">
-        <v>933</v>
+        <v>258</v>
+      </c>
+      <c r="B266" s="11">
+        <v>943</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="B267" s="12">
-        <v>1847</v>
+        <v>259</v>
+      </c>
+      <c r="B267" s="11">
+        <v>1896</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="B268" s="12">
-        <v>1231</v>
+        <v>260</v>
+      </c>
+      <c r="B268" s="11">
+        <v>1263</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A269" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="B269" s="12">
-        <v>1195</v>
+        <v>261</v>
+      </c>
+      <c r="B269" s="11">
+        <v>1219</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="B270" s="12">
-        <v>1440</v>
+        <v>262</v>
+      </c>
+      <c r="B270" s="11">
+        <v>1476</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="B271" s="12">
-        <v>34</v>
+        <v>263</v>
+      </c>
+      <c r="B271" s="11">
+        <v>35</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="B272" s="12">
+        <v>264</v>
+      </c>
+      <c r="B272" s="11">
         <v>26</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A273" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="B273" s="12">
+        <v>265</v>
+      </c>
+      <c r="B273" s="11">
         <v>25</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="B274" s="12">
-        <v>25</v>
+        <v>266</v>
+      </c>
+      <c r="B274" s="11">
+        <v>26</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="B275" s="12">
-        <v>25</v>
+        <v>267</v>
+      </c>
+      <c r="B275" s="11">
+        <v>26</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="B276" s="12">
-        <v>524</v>
+        <v>268</v>
+      </c>
+      <c r="B276" s="11">
+        <v>552</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A277" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="B277" s="12">
-        <v>302</v>
+        <v>269</v>
+      </c>
+      <c r="B277" s="11">
+        <v>297</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A278" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="B278" s="12">
-        <v>346</v>
+        <v>270</v>
+      </c>
+      <c r="B278" s="11">
+        <v>372</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="B279" s="12">
-        <v>316</v>
+        <v>271</v>
+      </c>
+      <c r="B279" s="11">
+        <v>348</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="B280" s="12">
+        <v>272</v>
+      </c>
+      <c r="B280" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A281" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="B281" s="12">
+        <v>273</v>
+      </c>
+      <c r="B281" s="11">
         <v>95</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A282" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="B282" s="12">
-        <v>47</v>
+        <v>274</v>
+      </c>
+      <c r="B282" s="11">
+        <v>46</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A283" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="B283" s="12">
-        <v>49</v>
+        <v>275</v>
+      </c>
+      <c r="B283" s="11">
+        <v>50</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A284" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="B284" s="12">
+        <v>276</v>
+      </c>
+      <c r="B284" s="11">
         <v>12</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A285" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="B285" s="12">
-        <v>27</v>
+        <v>277</v>
+      </c>
+      <c r="B285" s="11">
+        <v>25</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="B286" s="12">
-        <v>5677</v>
+        <v>278</v>
+      </c>
+      <c r="B286" s="11">
+        <v>5748</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="B287" s="12">
+        <v>279</v>
+      </c>
+      <c r="B287" s="11">
         <v>17</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A288" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="B288" s="12">
-        <v>4652</v>
+        <v>280</v>
+      </c>
+      <c r="B288" s="11">
+        <v>4704</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="B289" s="12">
-        <v>1404</v>
+        <v>281</v>
+      </c>
+      <c r="B289" s="11">
+        <v>1422</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A290" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="B290" s="12">
-        <v>234</v>
+        <v>282</v>
+      </c>
+      <c r="B290" s="11">
+        <v>229</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="B291" s="12">
-        <v>7574</v>
+        <v>283</v>
+      </c>
+      <c r="B291" s="11">
+        <v>7664</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A292" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="B292" s="12">
-        <v>4436</v>
+        <v>284</v>
+      </c>
+      <c r="B292" s="11">
+        <v>4480</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A293" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="B293" s="12">
+        <v>285</v>
+      </c>
+      <c r="B293" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="B294" s="12">
-        <v>11031</v>
+        <v>286</v>
+      </c>
+      <c r="B294" s="11">
+        <v>11160</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="B295" s="12">
-        <v>1159</v>
+        <v>287</v>
+      </c>
+      <c r="B295" s="11">
+        <v>1150</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="B296" s="12">
-        <v>5619</v>
+        <v>288</v>
+      </c>
+      <c r="B296" s="11">
+        <v>5685</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="B297" s="12">
-        <v>3666</v>
+        <v>289</v>
+      </c>
+      <c r="B297" s="11">
+        <v>3707</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="B298" s="12">
-        <v>1450</v>
+        <v>290</v>
+      </c>
+      <c r="B298" s="11">
+        <v>1470</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="B299" s="12">
+        <v>291</v>
+      </c>
+      <c r="B299" s="11">
         <v>84</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="B300" s="12">
-        <v>717</v>
+        <v>292</v>
+      </c>
+      <c r="B300" s="11">
+        <v>723</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="B301" s="12">
-        <v>8478</v>
+        <v>293</v>
+      </c>
+      <c r="B301" s="11">
+        <v>8572</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="B302" s="12">
-        <v>4138</v>
+        <v>294</v>
+      </c>
+      <c r="B302" s="11">
+        <v>4179</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="B303" s="12">
-        <v>5034</v>
+        <v>295</v>
+      </c>
+      <c r="B303" s="11">
+        <v>5084</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="B304" s="11">
+        <v>2381</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A305" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="B304" s="12">
-        <v>2333</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A305" s="9" t="s">
+      <c r="B305" s="11">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A306" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="B305" s="12">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A306" s="9" t="s">
+      <c r="B306" s="11">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A307" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="B306" s="12">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A307" s="9" t="s">
+      <c r="B307" s="11">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A308" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="B307" s="12">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A308" s="9" t="s">
+      <c r="B308" s="11">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A309" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="B308" s="12">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A309" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="B309" s="12">
+      <c r="B309" s="11">
         <v>18</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A310" s="1"/>
-      <c r="B310" s="13"/>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B310" s="12"/>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B311" s="12"/>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A312" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="B311" s="13"/>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A312" s="5" t="s">
+      <c r="B312" s="12"/>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A313" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B312" s="13"/>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A313" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="B313" s="13"/>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B313" s="12"/>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314" s="10"/>
-      <c r="B314" s="14"/>
-      <c r="C314" s="11"/>
+      <c r="B314" s="13"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:B5" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/dados/dados.xlsx
+++ b/dados/dados.xlsx
@@ -5,19 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\04 - Relatórios\Relatórios ROTINA\02 - Relatórios\2026\06 - Junho\ROTINA 2026_06_22\Formatados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\04 - Relatórios\Relatórios ROTINA\02 - Relatórios\2026\06 - Junho\ROTINA 2026_06_29\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{255C5465-FC7C-4FD4-9210-8C3E4D1945EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC2039D6-665C-41B8-9287-3DEDE130AD0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$5:$B$5</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -47,7 +44,7 @@
     <t>1. QUANTIDADE DE ESCOLAS NA REDE</t>
   </si>
   <si>
-    <t>1.1. QUANTIDADE DE ESCOLAS COM MATRÍCULA ATIVA EM 22/06/2026</t>
+    <t>1.1. QUANTIDADE DE ESCOLAS COM MATRÍCULA ATIVA EM 29/06/2026</t>
   </si>
   <si>
     <t>1.1.1. Quantidade de escolas com oferta de Ensino Fundamental</t>
@@ -947,16 +944,16 @@
     <t>SÍNTESE GERAL DA REDE ESTADUAL DE ENSINO</t>
   </si>
   <si>
+    <t>4.8 Quantidade de alunos público-alvo do AEE - Educação Especial (alunos com deficiência)</t>
+  </si>
+  <si>
     <t>FONTE: SEGES</t>
   </si>
   <si>
-    <t>DATA: 22/06/2026</t>
+    <t>DATA: 29/06/2026</t>
   </si>
   <si>
     <t>GEI/SEE/EAARAÚJO</t>
-  </si>
-  <si>
-    <t>4.8 Quantidade de alunos público-alvo do Atendimento Educacional Especializado - AEE (alunos com deficiência)</t>
   </si>
 </sst>
 </file>
@@ -965,7 +962,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -1114,7 +1111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1138,19 +1135,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1189,7 +1187,7 @@
         <xdr:cNvPr id="3" name="Imagem 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{996C27DB-C451-739D-0F60-523EB2911BD7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47948ECB-99EF-FB69-D20A-0D1C807E1129}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1500,8 +1498,8 @@
   <dimension ref="A1:C314"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="16.5" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="112.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="109.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3.7109375" style="1" customWidth="1"/>
     <col min="4" max="16384" width="11.42578125" style="8" hidden="1"/>
   </cols>
@@ -1509,10 +1507,10 @@
     <row r="1" spans="1:3" s="1" customFormat="1" ht="82.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:3" s="1" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:3" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>302</v>
       </c>
-      <c r="B3" s="15"/>
+      <c r="B3" s="16"/>
       <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1525,29 +1523,29 @@
       </c>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:3" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
+    <row r="6" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="18">
         <v>384</v>
       </c>
-      <c r="C6" s="18"/>
-    </row>
-    <row r="7" spans="1:3" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+      <c r="C6" s="19"/>
+    </row>
+    <row r="7" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="22">
         <v>383</v>
       </c>
-      <c r="C7" s="18"/>
+      <c r="C7" s="19"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="12">
         <v>267</v>
       </c>
     </row>
@@ -1555,7 +1553,7 @@
       <c r="A9" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="12">
         <v>98</v>
       </c>
     </row>
@@ -1563,7 +1561,7 @@
       <c r="A10" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="12">
         <v>235</v>
       </c>
     </row>
@@ -1571,7 +1569,7 @@
       <c r="A11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="12">
         <v>288</v>
       </c>
     </row>
@@ -1579,7 +1577,7 @@
       <c r="A12" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="12">
         <v>280</v>
       </c>
     </row>
@@ -1587,7 +1585,7 @@
       <c r="A13" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="12">
         <v>148</v>
       </c>
     </row>
@@ -1595,7 +1593,7 @@
       <c r="A14" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="12">
         <v>18</v>
       </c>
     </row>
@@ -1603,7 +1601,7 @@
       <c r="A15" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="12">
         <v>171</v>
       </c>
     </row>
@@ -1611,7 +1609,7 @@
       <c r="A16" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="12">
         <v>26</v>
       </c>
     </row>
@@ -1619,7 +1617,7 @@
       <c r="A17" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="12">
         <v>94</v>
       </c>
     </row>
@@ -1627,7 +1625,7 @@
       <c r="A18" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="12">
         <v>139</v>
       </c>
     </row>
@@ -1635,7 +1633,7 @@
       <c r="A19" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="12">
         <v>2</v>
       </c>
     </row>
@@ -1643,7 +1641,7 @@
       <c r="A20" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="12">
         <v>35</v>
       </c>
     </row>
@@ -1651,7 +1649,7 @@
       <c r="A21" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="12">
         <v>6</v>
       </c>
     </row>
@@ -1659,7 +1657,7 @@
       <c r="A22" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="12">
         <v>307</v>
       </c>
     </row>
@@ -1667,7 +1665,7 @@
       <c r="A23" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="12">
         <v>76</v>
       </c>
     </row>
@@ -1675,7 +1673,7 @@
       <c r="A24" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="12">
         <v>234</v>
       </c>
     </row>
@@ -1683,7 +1681,7 @@
       <c r="A25" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="12">
         <v>154</v>
       </c>
     </row>
@@ -1691,7 +1689,7 @@
       <c r="A26" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="12">
         <v>53</v>
       </c>
     </row>
@@ -1699,7 +1697,7 @@
       <c r="A27" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="12">
         <v>5</v>
       </c>
     </row>
@@ -1707,7 +1705,7 @@
       <c r="A28" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="12">
         <v>40</v>
       </c>
     </row>
@@ -1715,7 +1713,7 @@
       <c r="A29" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="12">
         <v>355</v>
       </c>
     </row>
@@ -1723,15 +1721,15 @@
       <c r="A30" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="11">
-        <v>220</v>
+      <c r="B30" s="12">
+        <v>221</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="12">
         <v>232</v>
       </c>
     </row>
@@ -1739,7 +1737,7 @@
       <c r="A32" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="11">
+      <c r="B32" s="12">
         <v>168</v>
       </c>
     </row>
@@ -1747,7 +1745,7 @@
       <c r="A33" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="12">
         <v>37</v>
       </c>
     </row>
@@ -1755,7 +1753,7 @@
       <c r="A34" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="12">
         <v>25</v>
       </c>
     </row>
@@ -1763,7 +1761,7 @@
       <c r="A35" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="12">
         <v>10</v>
       </c>
     </row>
@@ -1771,7 +1769,7 @@
       <c r="A36" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1779,7 +1777,7 @@
       <c r="A37" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B37" s="11">
+      <c r="B37" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1787,64 +1785,64 @@
       <c r="A38" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="12" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="20" t="s">
+    <row r="39" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B39" s="21">
-        <v>14860</v>
-      </c>
-      <c r="C39" s="18"/>
+      <c r="B39" s="22">
+        <v>14957</v>
+      </c>
+      <c r="C39" s="19"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="11">
-        <v>6944</v>
+      <c r="B40" s="12">
+        <v>7030</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="11">
-        <v>754</v>
+      <c r="B41" s="12">
+        <v>768</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B42" s="11">
-        <v>7162</v>
+      <c r="B42" s="12">
+        <v>7159</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="11">
-        <v>2523</v>
+      <c r="B43" s="12">
+        <v>2522</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="11">
-        <v>648</v>
+      <c r="B44" s="12">
+        <v>647</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B45" s="11">
+      <c r="B45" s="12">
         <v>125</v>
       </c>
     </row>
@@ -1852,7 +1850,7 @@
       <c r="A46" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B46" s="11">
+      <c r="B46" s="12">
         <v>132</v>
       </c>
     </row>
@@ -1860,7 +1858,7 @@
       <c r="A47" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="11">
+      <c r="B47" s="12">
         <v>131</v>
       </c>
     </row>
@@ -1868,7 +1866,7 @@
       <c r="A48" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="11">
+      <c r="B48" s="12">
         <v>124</v>
       </c>
     </row>
@@ -1876,15 +1874,15 @@
       <c r="A49" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B49" s="11">
-        <v>136</v>
+      <c r="B49" s="12">
+        <v>135</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B50" s="11">
+      <c r="B50" s="12">
         <v>1875</v>
       </c>
     </row>
@@ -1892,7 +1890,7 @@
       <c r="A51" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="11">
+      <c r="B51" s="12">
         <v>447</v>
       </c>
     </row>
@@ -1900,7 +1898,7 @@
       <c r="A52" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B52" s="11">
+      <c r="B52" s="12">
         <v>453</v>
       </c>
     </row>
@@ -1908,7 +1906,7 @@
       <c r="A53" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="11">
+      <c r="B53" s="12">
         <v>460</v>
       </c>
     </row>
@@ -1916,7 +1914,7 @@
       <c r="A54" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B54" s="11">
+      <c r="B54" s="12">
         <v>515</v>
       </c>
     </row>
@@ -1924,31 +1922,31 @@
       <c r="A55" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B55" s="11">
-        <v>3463</v>
+      <c r="B55" s="12">
+        <v>3461</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B56" s="11">
-        <v>2625</v>
+      <c r="B56" s="12">
+        <v>2624</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B57" s="11">
-        <v>943</v>
+      <c r="B57" s="12">
+        <v>942</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B58" s="11">
+      <c r="B58" s="12">
         <v>884</v>
       </c>
     </row>
@@ -1956,7 +1954,7 @@
       <c r="A59" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B59" s="11">
+      <c r="B59" s="12">
         <v>798</v>
       </c>
     </row>
@@ -1964,7 +1962,7 @@
       <c r="A60" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B60" s="11">
+      <c r="B60" s="12">
         <v>0</v>
       </c>
     </row>
@@ -1972,23 +1970,23 @@
       <c r="A61" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B61" s="11">
-        <v>838</v>
+      <c r="B61" s="12">
+        <v>837</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B62" s="11">
-        <v>286</v>
+      <c r="B62" s="12">
+        <v>285</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B63" s="11">
+      <c r="B63" s="12">
         <v>278</v>
       </c>
     </row>
@@ -1996,7 +1994,7 @@
       <c r="A64" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B64" s="11">
+      <c r="B64" s="12">
         <v>274</v>
       </c>
     </row>
@@ -2004,7 +2002,7 @@
       <c r="A65" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B65" s="11">
+      <c r="B65" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2012,7 +2010,7 @@
       <c r="A66" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B66" s="11">
+      <c r="B66" s="12">
         <v>18</v>
       </c>
     </row>
@@ -2020,7 +2018,7 @@
       <c r="A67" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B67" s="11">
+      <c r="B67" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2028,7 +2026,7 @@
       <c r="A68" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B68" s="11">
+      <c r="B68" s="12">
         <v>18</v>
       </c>
     </row>
@@ -2036,7 +2034,7 @@
       <c r="A69" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B69" s="11">
+      <c r="B69" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2044,7 +2042,7 @@
       <c r="A70" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B70" s="11">
+      <c r="B70" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2052,7 +2050,7 @@
       <c r="A71" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B71" s="11">
+      <c r="B71" s="12">
         <v>1158</v>
       </c>
     </row>
@@ -2060,7 +2058,7 @@
       <c r="A72" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B72" s="11">
+      <c r="B72" s="12">
         <v>172</v>
       </c>
     </row>
@@ -2068,7 +2066,7 @@
       <c r="A73" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B73" s="11">
+      <c r="B73" s="12">
         <v>39</v>
       </c>
     </row>
@@ -2076,23 +2074,23 @@
       <c r="A74" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="B74" s="11">
-        <v>45</v>
+      <c r="B74" s="12">
+        <v>44</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B75" s="11">
-        <v>42</v>
+      <c r="B75" s="12">
+        <v>43</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B76" s="11">
+      <c r="B76" s="12">
         <v>46</v>
       </c>
     </row>
@@ -2100,15 +2098,15 @@
       <c r="A77" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B77" s="11">
-        <v>438</v>
+      <c r="B77" s="12">
+        <v>439</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B78" s="11">
+      <c r="B78" s="12">
         <v>93</v>
       </c>
     </row>
@@ -2116,47 +2114,47 @@
       <c r="A79" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B79" s="11">
-        <v>104</v>
+      <c r="B79" s="12">
+        <v>105</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B80" s="11">
-        <v>120</v>
+      <c r="B80" s="12">
+        <v>119</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B81" s="11">
-        <v>121</v>
+      <c r="B81" s="12">
+        <v>122</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B82" s="11">
-        <v>430</v>
+      <c r="B82" s="12">
+        <v>429</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B83" s="11">
-        <v>133</v>
+      <c r="B83" s="12">
+        <v>132</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B84" s="11">
+      <c r="B84" s="12">
         <v>136</v>
       </c>
     </row>
@@ -2164,7 +2162,7 @@
       <c r="A85" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B85" s="11">
+      <c r="B85" s="12">
         <v>161</v>
       </c>
     </row>
@@ -2172,7 +2170,7 @@
       <c r="A86" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B86" s="11">
+      <c r="B86" s="12">
         <v>8</v>
       </c>
     </row>
@@ -2180,7 +2178,7 @@
       <c r="A87" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B87" s="11">
+      <c r="B87" s="12">
         <v>2</v>
       </c>
     </row>
@@ -2188,7 +2186,7 @@
       <c r="A88" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B88" s="11">
+      <c r="B88" s="12">
         <v>2</v>
       </c>
     </row>
@@ -2196,7 +2194,7 @@
       <c r="A89" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B89" s="11">
+      <c r="B89" s="12">
         <v>2</v>
       </c>
     </row>
@@ -2204,7 +2202,7 @@
       <c r="A90" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B90" s="11">
+      <c r="B90" s="12">
         <v>2</v>
       </c>
     </row>
@@ -2212,7 +2210,7 @@
       <c r="A91" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B91" s="11">
+      <c r="B91" s="12">
         <v>99</v>
       </c>
     </row>
@@ -2220,7 +2218,7 @@
       <c r="A92" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="B92" s="11">
+      <c r="B92" s="12">
         <v>30</v>
       </c>
     </row>
@@ -2228,7 +2226,7 @@
       <c r="A93" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B93" s="11">
+      <c r="B93" s="12">
         <v>34</v>
       </c>
     </row>
@@ -2236,7 +2234,7 @@
       <c r="A94" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B94" s="11">
+      <c r="B94" s="12">
         <v>35</v>
       </c>
     </row>
@@ -2244,7 +2242,7 @@
       <c r="A95" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B95" s="11">
+      <c r="B95" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2252,7 +2250,7 @@
       <c r="A96" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B96" s="11">
+      <c r="B96" s="12">
         <v>11</v>
       </c>
     </row>
@@ -2260,7 +2258,7 @@
       <c r="A97" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B97" s="11">
+      <c r="B97" s="12">
         <v>4</v>
       </c>
     </row>
@@ -2268,7 +2266,7 @@
       <c r="A98" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B98" s="11">
+      <c r="B98" s="12">
         <v>5</v>
       </c>
     </row>
@@ -2276,7 +2274,7 @@
       <c r="A99" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B99" s="11">
+      <c r="B99" s="12">
         <v>2</v>
       </c>
     </row>
@@ -2284,47 +2282,47 @@
       <c r="A100" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B100" s="11">
-        <v>13538</v>
+      <c r="B100" s="12">
+        <v>13628</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B101" s="11">
-        <v>1322</v>
+      <c r="B101" s="12">
+        <v>1329</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B102" s="11">
-        <v>2394</v>
+      <c r="B102" s="12">
+        <v>2392</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B103" s="11">
-        <v>1637</v>
+      <c r="B103" s="12">
+        <v>1636</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B104" s="11">
-        <v>484</v>
+      <c r="B104" s="12">
+        <v>483</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="B105" s="11">
+      <c r="B105" s="12">
         <v>8</v>
       </c>
     </row>
@@ -2332,7 +2330,7 @@
       <c r="A106" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="B106" s="11">
+      <c r="B106" s="12">
         <v>265</v>
       </c>
     </row>
@@ -2340,47 +2338,47 @@
       <c r="A107" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B107" s="11">
-        <v>4768</v>
+      <c r="B107" s="12">
+        <v>4767</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B108" s="11">
-        <v>1955</v>
+      <c r="B108" s="12">
+        <v>1957</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="B109" s="11">
-        <v>1930</v>
+      <c r="B109" s="12">
+        <v>1929</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="B110" s="11">
-        <v>883</v>
+      <c r="B110" s="12">
+        <v>881</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B111" s="11">
-        <v>639</v>
+      <c r="B111" s="12">
+        <v>642</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B112" s="11">
+      <c r="B112" s="12">
         <v>295</v>
       </c>
     </row>
@@ -2388,23 +2386,23 @@
       <c r="A113" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B113" s="11">
-        <v>285</v>
+      <c r="B113" s="12">
+        <v>286</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="B114" s="11">
-        <v>48</v>
+      <c r="B114" s="12">
+        <v>50</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B115" s="11">
+      <c r="B115" s="12">
         <v>11</v>
       </c>
     </row>
@@ -2412,281 +2410,281 @@
       <c r="A116" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B116" s="11" t="s">
+      <c r="B116" s="12" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="117" spans="1:3" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="20" t="s">
+    <row r="117" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="B117" s="21">
-        <v>216936</v>
-      </c>
-      <c r="C117" s="18"/>
+      <c r="B117" s="22">
+        <v>216954</v>
+      </c>
+      <c r="C117" s="19"/>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B118" s="11">
-        <v>182019</v>
+      <c r="B118" s="12">
+        <v>181623</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="B119" s="11">
-        <v>18875</v>
+      <c r="B119" s="12">
+        <v>19085</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="B120" s="11">
-        <v>16042</v>
+      <c r="B120" s="12">
+        <v>16246</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B121" s="11" t="s">
+      <c r="B121" s="12" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="122" spans="1:3" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="20" t="s">
+    <row r="122" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B122" s="21">
-        <v>181924</v>
-      </c>
-      <c r="C122" s="18"/>
+      <c r="B122" s="22">
+        <v>181546</v>
+      </c>
+      <c r="C122" s="19"/>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="B123" s="11">
-        <v>10624</v>
+      <c r="B123" s="12">
+        <v>10736</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B124" s="11">
-        <v>14832</v>
+      <c r="B124" s="12">
+        <v>14988</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B125" s="11">
-        <v>181665</v>
+      <c r="B125" s="12">
+        <v>181271</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B126" s="11">
-        <v>51355</v>
+      <c r="B126" s="12">
+        <v>51371</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B127" s="11">
-        <v>48168</v>
+      <c r="B127" s="12">
+        <v>48089</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B128" s="11">
-        <v>12909</v>
+      <c r="B128" s="12">
+        <v>12687</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B129" s="11">
-        <v>48290</v>
+      <c r="B129" s="12">
+        <v>48226</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B130" s="11">
-        <v>14886</v>
+      <c r="B130" s="12">
+        <v>14861</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B131" s="11">
-        <v>168</v>
+      <c r="B131" s="12">
+        <v>166</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B132" s="11">
-        <v>6243</v>
+      <c r="B132" s="12">
+        <v>6223</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B133" s="11">
-        <v>63148</v>
+      <c r="B133" s="12">
+        <v>63109</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B134" s="11">
-        <v>10861</v>
+      <c r="B134" s="12">
+        <v>10853</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B135" s="11">
-        <v>1942</v>
+      <c r="B135" s="12">
+        <v>1946</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="B136" s="11">
-        <v>2164</v>
+      <c r="B136" s="12">
+        <v>2158</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="B137" s="11">
-        <v>2136</v>
+      <c r="B137" s="12">
+        <v>2133</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B138" s="11">
-        <v>2122</v>
+      <c r="B138" s="12">
+        <v>2123</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B139" s="11">
-        <v>2497</v>
+      <c r="B139" s="12">
+        <v>2493</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B140" s="11">
-        <v>52287</v>
+      <c r="B140" s="12">
+        <v>52256</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="B141" s="11">
-        <v>12277</v>
+      <c r="B141" s="12">
+        <v>12274</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B142" s="11">
-        <v>12503</v>
+      <c r="B142" s="12">
+        <v>12487</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="B143" s="11">
-        <v>13110</v>
+      <c r="B143" s="12">
+        <v>13086</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="B144" s="11">
-        <v>14397</v>
+      <c r="B144" s="12">
+        <v>14409</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="B145" s="11">
-        <v>104989</v>
+      <c r="B145" s="12">
+        <v>104923</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B146" s="11">
-        <v>80100</v>
+      <c r="B146" s="12">
+        <v>80080</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B147" s="11">
-        <v>30009</v>
+      <c r="B147" s="12">
+        <v>30004</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B148" s="11">
-        <v>27578</v>
+      <c r="B148" s="12">
+        <v>27569</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="B149" s="11">
-        <v>22513</v>
+      <c r="B149" s="12">
+        <v>22507</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="B150" s="11">
+      <c r="B150" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2694,39 +2692,39 @@
       <c r="A151" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="B151" s="11">
-        <v>24889</v>
+      <c r="B151" s="12">
+        <v>24843</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="B152" s="11">
-        <v>9835</v>
+      <c r="B152" s="12">
+        <v>9813</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B153" s="11">
-        <v>7939</v>
+      <c r="B153" s="12">
+        <v>7916</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="B154" s="11">
-        <v>7115</v>
+      <c r="B154" s="12">
+        <v>7114</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="B155" s="11">
+      <c r="B155" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2734,15 +2732,15 @@
       <c r="A156" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="B156" s="11">
-        <v>361</v>
+      <c r="B156" s="12">
+        <v>358</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="B157" s="11">
+      <c r="B157" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2750,15 +2748,15 @@
       <c r="A158" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="B158" s="11">
-        <v>361</v>
+      <c r="B158" s="12">
+        <v>358</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="B159" s="11">
+      <c r="B159" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2766,7 +2764,7 @@
       <c r="A160" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="B160" s="11">
+      <c r="B160" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2774,199 +2772,199 @@
       <c r="A161" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B161" s="11">
-        <v>13521</v>
+      <c r="B161" s="12">
+        <v>13233</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="B162" s="11">
-        <v>752</v>
+      <c r="B162" s="12">
+        <v>735</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="B163" s="11">
-        <v>144</v>
+      <c r="B163" s="12">
+        <v>141</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="B164" s="11">
-        <v>178</v>
+      <c r="B164" s="12">
+        <v>171</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="B165" s="11">
-        <v>186</v>
+      <c r="B165" s="12">
+        <v>183</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="B166" s="11">
-        <v>244</v>
+      <c r="B166" s="12">
+        <v>240</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="B167" s="11">
-        <v>3545</v>
+      <c r="B167" s="12">
+        <v>3474</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="B168" s="11">
-        <v>525</v>
+      <c r="B168" s="12">
+        <v>514</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="B169" s="11">
-        <v>675</v>
+      <c r="B169" s="12">
+        <v>663</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="B170" s="11">
-        <v>1056</v>
+      <c r="B170" s="12">
+        <v>1037</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="B171" s="11">
-        <v>1289</v>
+      <c r="B171" s="12">
+        <v>1260</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="B172" s="11">
-        <v>7174</v>
+      <c r="B172" s="12">
+        <v>7007</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="B173" s="11">
-        <v>1592</v>
+      <c r="B173" s="12">
+        <v>1541</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="B174" s="11">
-        <v>2139</v>
+      <c r="B174" s="12">
+        <v>2097</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B175" s="11">
-        <v>3443</v>
+      <c r="B175" s="12">
+        <v>3369</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="B176" s="11">
-        <v>85</v>
+      <c r="B176" s="12">
+        <v>92</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="B177" s="11">
-        <v>11</v>
+      <c r="B177" s="12">
+        <v>12</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B178" s="11">
-        <v>21</v>
+      <c r="B178" s="12">
+        <v>22</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B179" s="11">
-        <v>31</v>
+      <c r="B179" s="12">
+        <v>33</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B180" s="11">
-        <v>22</v>
+      <c r="B180" s="12">
+        <v>25</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="B181" s="11">
-        <v>1746</v>
+      <c r="B181" s="12">
+        <v>1708</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="B182" s="11">
-        <v>446</v>
+      <c r="B182" s="12">
+        <v>427</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="B183" s="11">
-        <v>646</v>
+      <c r="B183" s="12">
+        <v>639</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="B184" s="11">
-        <v>654</v>
+      <c r="B184" s="12">
+        <v>642</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="B185" s="11">
+      <c r="B185" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2974,111 +2972,111 @@
       <c r="A186" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B186" s="11">
-        <v>219</v>
+      <c r="B186" s="12">
+        <v>217</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="B187" s="11">
-        <v>100</v>
+      <c r="B187" s="12">
+        <v>99</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B188" s="11">
-        <v>83</v>
+      <c r="B188" s="12">
+        <v>82</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="B189" s="11">
+      <c r="B189" s="12">
         <v>36</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="B190" s="11">
-        <v>12683</v>
+        <v>303</v>
+      </c>
+      <c r="B190" s="12">
+        <v>12730</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="B191" s="11">
-        <v>359</v>
+      <c r="B191" s="12">
+        <v>356</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="B192" s="11">
-        <v>50539</v>
+      <c r="B192" s="12">
+        <v>50497</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="B193" s="11">
-        <v>590</v>
+      <c r="B193" s="12">
+        <v>547</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="B194" s="11">
-        <v>111647</v>
+      <c r="B194" s="12">
+        <v>111418</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="B195" s="11">
-        <v>18718</v>
+      <c r="B195" s="12">
+        <v>18649</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="B196" s="11">
-        <v>71</v>
+      <c r="B196" s="12">
+        <v>79</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="B197" s="11">
-        <v>90445</v>
+      <c r="B197" s="12">
+        <v>90255</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="B198" s="11">
-        <v>91477</v>
+      <c r="B198" s="12">
+        <v>91289</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="B199" s="11">
+      <c r="B199" s="12">
         <v>2</v>
       </c>
     </row>
@@ -3086,119 +3084,119 @@
       <c r="A200" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="B200" s="11">
-        <v>170606</v>
+      <c r="B200" s="12">
+        <v>170304</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="B201" s="11">
-        <v>11387</v>
+      <c r="B201" s="12">
+        <v>11312</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="B202" s="11">
-        <v>69587</v>
+      <c r="B202" s="12">
+        <v>69476</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="B203" s="11">
-        <v>48290</v>
+      <c r="B203" s="12">
+        <v>48226</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="B204" s="11">
-        <v>14886</v>
+      <c r="B204" s="12">
+        <v>14861</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="B205" s="11">
-        <v>168</v>
+      <c r="B205" s="12">
+        <v>166</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="B206" s="11">
-        <v>6243</v>
+      <c r="B206" s="12">
+        <v>6223</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="B207" s="11">
-        <v>112294</v>
+      <c r="B207" s="12">
+        <v>112011</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="B208" s="11">
-        <v>51355</v>
+      <c r="B208" s="12">
+        <v>51371</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="B209" s="11">
-        <v>48168</v>
+      <c r="B209" s="12">
+        <v>48089</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="B210" s="11">
-        <v>12909</v>
+      <c r="B210" s="12">
+        <v>12687</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="B211" s="11">
-        <v>6157</v>
+      <c r="B211" s="12">
+        <v>6130</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="B212" s="11">
-        <v>1403</v>
+      <c r="B212" s="12">
+        <v>1382</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="B213" s="11">
-        <v>4300</v>
+      <c r="B213" s="12">
+        <v>4297</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="B214" s="11">
+      <c r="B214" s="12">
         <v>329</v>
       </c>
     </row>
@@ -3206,96 +3204,96 @@
       <c r="A215" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B215" s="11">
-        <v>125</v>
+      <c r="B215" s="12">
+        <v>122</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B216" s="11" t="s">
+      <c r="B216" s="12" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="217" spans="1:3" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="20" t="s">
+    <row r="217" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A217" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="B217" s="21">
-        <v>13072</v>
-      </c>
-      <c r="C217" s="18"/>
+      <c r="B217" s="22">
+        <v>13123</v>
+      </c>
+      <c r="C217" s="19"/>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="B218" s="11">
-        <v>912</v>
+      <c r="B218" s="12">
+        <v>923</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="B219" s="11">
-        <v>265</v>
+      <c r="B219" s="12">
+        <v>272</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B220" s="11">
-        <v>12145</v>
+      <c r="B220" s="12">
+        <v>12185</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="B221" s="11">
-        <v>4179</v>
+      <c r="B221" s="12">
+        <v>4195</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="B222" s="11">
-        <v>5084</v>
+      <c r="B222" s="12">
+        <v>5105</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="B223" s="11">
-        <v>2381</v>
+      <c r="B223" s="12">
+        <v>2393</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="B224" s="11">
-        <v>3707</v>
+      <c r="B224" s="12">
+        <v>3714</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="B225" s="11">
-        <v>1470</v>
+      <c r="B225" s="12">
+        <v>1480</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="B226" s="11">
+      <c r="B226" s="12">
         <v>84</v>
       </c>
     </row>
@@ -3303,47 +3301,47 @@
       <c r="A227" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="B227" s="11">
-        <v>723</v>
+      <c r="B227" s="12">
+        <v>721</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="B228" s="11">
-        <v>5173</v>
+      <c r="B228" s="12">
+        <v>5194</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="B229" s="11">
-        <v>876</v>
+      <c r="B229" s="12">
+        <v>877</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B230" s="11">
-        <v>378</v>
+      <c r="B230" s="12">
+        <v>380</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="B231" s="11">
-        <v>393</v>
+      <c r="B231" s="12">
+        <v>395</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="B232" s="11">
+      <c r="B232" s="12">
         <v>408</v>
       </c>
     </row>
@@ -3351,103 +3349,103 @@
       <c r="A233" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="B233" s="11">
-        <v>396</v>
+      <c r="B233" s="12">
+        <v>397</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="B234" s="11">
-        <v>436</v>
+      <c r="B234" s="12">
+        <v>435</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="B235" s="11">
-        <v>4497</v>
+      <c r="B235" s="12">
+        <v>4518</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="B236" s="11">
-        <v>2458</v>
+      <c r="B236" s="12">
+        <v>2469</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="B237" s="11">
-        <v>2661</v>
+      <c r="B237" s="12">
+        <v>2674</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="B238" s="11">
-        <v>2875</v>
+      <c r="B238" s="12">
+        <v>2888</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="B239" s="11">
-        <v>2968</v>
+      <c r="B239" s="12">
+        <v>2975</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="B240" s="11">
-        <v>8772</v>
+      <c r="B240" s="12">
+        <v>8796</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="B241" s="11">
-        <v>7306</v>
+      <c r="B241" s="12">
+        <v>7322</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="B242" s="11">
-        <v>5182</v>
+      <c r="B242" s="12">
+        <v>5193</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="B243" s="11">
-        <v>5594</v>
+      <c r="B243" s="12">
+        <v>5610</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="B244" s="11">
-        <v>5037</v>
+      <c r="B244" s="12">
+        <v>5051</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="B245" s="11">
+      <c r="B245" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3455,39 +3453,39 @@
       <c r="A246" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="B246" s="11">
-        <v>3630</v>
+      <c r="B246" s="12">
+        <v>3638</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="B247" s="11">
-        <v>2351</v>
+      <c r="B247" s="12">
+        <v>2359</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="B248" s="11">
-        <v>2073</v>
+      <c r="B248" s="12">
+        <v>2076</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="B249" s="11">
-        <v>2032</v>
+      <c r="B249" s="12">
+        <v>2029</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="B250" s="11">
+      <c r="B250" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3495,15 +3493,15 @@
       <c r="A251" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="B251" s="11">
-        <v>95</v>
+      <c r="B251" s="12">
+        <v>96</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="B252" s="11">
+      <c r="B252" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3511,15 +3509,15 @@
       <c r="A253" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="B253" s="11">
-        <v>95</v>
+      <c r="B253" s="12">
+        <v>96</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="B254" s="11">
+      <c r="B254" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3527,7 +3525,7 @@
       <c r="A255" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="B255" s="11">
+      <c r="B255" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3535,15 +3533,15 @@
       <c r="A256" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="B256" s="11">
-        <v>2569</v>
+      <c r="B256" s="12">
+        <v>2583</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="B257" s="11">
+      <c r="B257" s="12">
         <v>167</v>
       </c>
     </row>
@@ -3551,7 +3549,7 @@
       <c r="A258" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="B258" s="11">
+      <c r="B258" s="12">
         <v>127</v>
       </c>
     </row>
@@ -3559,7 +3557,7 @@
       <c r="A259" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="B259" s="11">
+      <c r="B259" s="12">
         <v>131</v>
       </c>
     </row>
@@ -3567,7 +3565,7 @@
       <c r="A260" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="B260" s="11">
+      <c r="B260" s="12">
         <v>140</v>
       </c>
     </row>
@@ -3575,7 +3573,7 @@
       <c r="A261" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="B261" s="11">
+      <c r="B261" s="12">
         <v>147</v>
       </c>
     </row>
@@ -3583,79 +3581,79 @@
       <c r="A262" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="B262" s="11">
-        <v>1048</v>
+      <c r="B262" s="12">
+        <v>1055</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="B263" s="11">
-        <v>690</v>
+      <c r="B263" s="12">
+        <v>695</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="B264" s="11">
-        <v>790</v>
+      <c r="B264" s="12">
+        <v>796</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="B265" s="11">
-        <v>928</v>
+      <c r="B265" s="12">
+        <v>935</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="B266" s="11">
-        <v>943</v>
+      <c r="B266" s="12">
+        <v>949</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="B267" s="11">
-        <v>1896</v>
+      <c r="B267" s="12">
+        <v>1907</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="B268" s="11">
-        <v>1263</v>
+      <c r="B268" s="12">
+        <v>1271</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A269" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="B269" s="11">
-        <v>1219</v>
+      <c r="B269" s="12">
+        <v>1227</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="B270" s="11">
-        <v>1476</v>
+      <c r="B270" s="12">
+        <v>1484</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="B271" s="11">
+      <c r="B271" s="12">
         <v>35</v>
       </c>
     </row>
@@ -3663,7 +3661,7 @@
       <c r="A272" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="B272" s="11">
+      <c r="B272" s="12">
         <v>26</v>
       </c>
     </row>
@@ -3671,7 +3669,7 @@
       <c r="A273" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="B273" s="11">
+      <c r="B273" s="12">
         <v>25</v>
       </c>
     </row>
@@ -3679,7 +3677,7 @@
       <c r="A274" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="B274" s="11">
+      <c r="B274" s="12">
         <v>26</v>
       </c>
     </row>
@@ -3687,7 +3685,7 @@
       <c r="A275" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="B275" s="11">
+      <c r="B275" s="12">
         <v>26</v>
       </c>
     </row>
@@ -3695,39 +3693,39 @@
       <c r="A276" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="B276" s="11">
-        <v>552</v>
+      <c r="B276" s="12">
+        <v>556</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A277" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="B277" s="11">
-        <v>297</v>
+      <c r="B277" s="12">
+        <v>298</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A278" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="B278" s="11">
-        <v>372</v>
+      <c r="B278" s="12">
+        <v>377</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="B279" s="11">
-        <v>348</v>
+      <c r="B279" s="12">
+        <v>351</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="B280" s="11">
+      <c r="B280" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3735,7 +3733,7 @@
       <c r="A281" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="B281" s="11">
+      <c r="B281" s="12">
         <v>95</v>
       </c>
     </row>
@@ -3743,7 +3741,7 @@
       <c r="A282" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="B282" s="11">
+      <c r="B282" s="12">
         <v>46</v>
       </c>
     </row>
@@ -3751,15 +3749,15 @@
       <c r="A283" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="B283" s="11">
-        <v>50</v>
+      <c r="B283" s="12">
+        <v>52</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A284" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="B284" s="11">
+      <c r="B284" s="12">
         <v>12</v>
       </c>
     </row>
@@ -3767,23 +3765,23 @@
       <c r="A285" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="B285" s="11">
-        <v>25</v>
+      <c r="B285" s="12">
+        <v>26</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="B286" s="11">
-        <v>5748</v>
+      <c r="B286" s="12">
+        <v>5758</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="B287" s="11">
+      <c r="B287" s="12">
         <v>17</v>
       </c>
     </row>
@@ -3791,95 +3789,95 @@
       <c r="A288" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="B288" s="11">
-        <v>4704</v>
+      <c r="B288" s="12">
+        <v>4724</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="B289" s="11">
-        <v>1422</v>
+      <c r="B289" s="12">
+        <v>1429</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A290" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="B290" s="11">
-        <v>229</v>
+      <c r="B290" s="12">
+        <v>231</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="B291" s="11">
-        <v>7664</v>
+      <c r="B291" s="12">
+        <v>7698</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A292" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="B292" s="11">
-        <v>4480</v>
+      <c r="B292" s="12">
+        <v>4487</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A293" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="B293" s="11">
-        <v>1</v>
+      <c r="B293" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="B294" s="11">
-        <v>11160</v>
+      <c r="B294" s="12">
+        <v>11198</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="B295" s="11">
-        <v>1150</v>
+      <c r="B295" s="12">
+        <v>1152</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="B296" s="11">
-        <v>5685</v>
+      <c r="B296" s="12">
+        <v>5701</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="B297" s="11">
-        <v>3707</v>
+      <c r="B297" s="12">
+        <v>3714</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="B298" s="11">
-        <v>1470</v>
+      <c r="B298" s="12">
+        <v>1480</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="B299" s="11">
+      <c r="B299" s="12">
         <v>84</v>
       </c>
     </row>
@@ -3887,110 +3885,110 @@
       <c r="A300" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="B300" s="11">
-        <v>723</v>
+      <c r="B300" s="12">
+        <v>721</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="B301" s="11">
-        <v>8572</v>
+      <c r="B301" s="12">
+        <v>8605</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="B302" s="11">
-        <v>4179</v>
+      <c r="B302" s="12">
+        <v>4195</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="B303" s="11">
-        <v>5084</v>
+      <c r="B303" s="12">
+        <v>5105</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="B304" s="11">
-        <v>2381</v>
-      </c>
-    </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B304" s="12">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="B305" s="11">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B305" s="12">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="B306" s="11">
+      <c r="B306" s="12">
         <v>234</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="B307" s="11">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B307" s="12">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="B308" s="11">
+      <c r="B308" s="12">
         <v>35</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="B309" s="11">
+      <c r="B309" s="12">
         <v>18</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" s="1"/>
-      <c r="B310" s="12"/>
-    </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B310" s="13"/>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B311" s="12"/>
-    </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+      <c r="B311" s="13"/>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="B312" s="12"/>
-    </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+      <c r="B312" s="13"/>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="B313" s="12"/>
-    </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
+        <v>306</v>
+      </c>
+      <c r="B313" s="13"/>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" s="10"/>
-      <c r="B314" s="13"/>
+      <c r="B314" s="14"/>
+      <c r="C314" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:B5" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
